--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119706741</v>
+        <v>119706939</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2257,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481017</v>
+        <v>481111</v>
       </c>
       <c r="R16" t="n">
-        <v>6784518</v>
+        <v>6784709</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2351,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119706939</v>
+        <v>119706741</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481111</v>
+        <v>481017</v>
       </c>
       <c r="R17" t="n">
-        <v>6784709</v>
+        <v>6784518</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119789016</v>
+        <v>119786836</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3851,25 +3851,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480995</v>
+        <v>481049</v>
       </c>
       <c r="R31" t="n">
-        <v>6784692</v>
+        <v>6784514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788950</v>
+        <v>119788312</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3953,38 +3953,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480996</v>
+        <v>481062</v>
       </c>
       <c r="R32" t="n">
-        <v>6784667</v>
+        <v>6784614</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,19 +4014,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4041,19 +4031,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119788519</v>
+        <v>119789016</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -4093,10 +4083,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481087</v>
+        <v>480995</v>
       </c>
       <c r="R33" t="n">
-        <v>6784724</v>
+        <v>6784692</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,10 +4145,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119786836</v>
+        <v>119788950</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4167,38 +4157,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481049</v>
+        <v>480996</v>
       </c>
       <c r="R34" t="n">
-        <v>6784514</v>
+        <v>6784667</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4228,9 +4218,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4245,22 +4245,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119788312</v>
+        <v>119788519</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4269,25 +4269,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481062</v>
+        <v>481087</v>
       </c>
       <c r="R35" t="n">
-        <v>6784614</v>
+        <v>6784724</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4347,12 +4347,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119788782</v>
+        <v>119787825</v>
       </c>
       <c r="B61" t="n">
-        <v>91863</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6988,43 +6988,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481195</v>
+        <v>481250</v>
       </c>
       <c r="R61" t="n">
-        <v>6784739</v>
+        <v>6784659</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7056,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7066,7 +7057,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7093,10 +7084,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119787825</v>
+        <v>119789066</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7109,21 +7100,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7133,10 +7124,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481250</v>
+        <v>480996</v>
       </c>
       <c r="R62" t="n">
-        <v>6784659</v>
+        <v>6784667</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7168,7 +7159,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7178,7 +7169,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7205,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119789066</v>
+        <v>119787807</v>
       </c>
       <c r="B63" t="n">
         <v>91856</v>
@@ -7245,10 +7236,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480996</v>
+        <v>481250</v>
       </c>
       <c r="R63" t="n">
-        <v>6784667</v>
+        <v>6784659</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7280,7 +7271,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7290,7 +7281,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7317,7 +7308,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119787807</v>
+        <v>119788082</v>
       </c>
       <c r="B64" t="n">
         <v>91856</v>
@@ -7353,14 +7344,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481250</v>
+        <v>481144</v>
       </c>
       <c r="R64" t="n">
-        <v>6784659</v>
+        <v>6784602</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7390,19 +7381,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7417,22 +7398,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119788082</v>
+        <v>119788782</v>
       </c>
       <c r="B65" t="n">
-        <v>91856</v>
+        <v>91863</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7445,34 +7426,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481144</v>
+        <v>481195</v>
       </c>
       <c r="R65" t="n">
-        <v>6784602</v>
+        <v>6784739</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7502,9 +7492,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7519,12 +7519,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8071,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119788662</v>
+        <v>119787774</v>
       </c>
       <c r="B71" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8083,25 +8083,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481133</v>
+        <v>481250</v>
       </c>
       <c r="R71" t="n">
-        <v>6784731</v>
+        <v>6784627</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8173,10 +8173,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119787774</v>
+        <v>119788662</v>
       </c>
       <c r="B72" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8185,25 +8185,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481250</v>
+        <v>481133</v>
       </c>
       <c r="R72" t="n">
-        <v>6784627</v>
+        <v>6784731</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9616,10 +9616,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788928</v>
+        <v>119789434</v>
       </c>
       <c r="B86" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9632,34 +9632,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481138</v>
+        <v>481002</v>
       </c>
       <c r="R86" t="n">
-        <v>6784747</v>
+        <v>6784693</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9689,9 +9694,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9706,22 +9721,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119789434</v>
+        <v>119788928</v>
       </c>
       <c r="B87" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9734,39 +9749,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481002</v>
+        <v>481138</v>
       </c>
       <c r="R87" t="n">
-        <v>6784693</v>
+        <v>6784747</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9796,19 +9806,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9823,12 +9823,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -2245,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119706939</v>
+        <v>119706741</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2257,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481111</v>
+        <v>481017</v>
       </c>
       <c r="R16" t="n">
-        <v>6784709</v>
+        <v>6784518</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2351,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119706741</v>
+        <v>119706939</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,25 +2363,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481017</v>
+        <v>481111</v>
       </c>
       <c r="R17" t="n">
-        <v>6784518</v>
+        <v>6784709</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119683447</v>
+        <v>119683370</v>
       </c>
       <c r="B2" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481045</v>
+        <v>481038</v>
       </c>
       <c r="R2" t="n">
-        <v>6784589</v>
+        <v>6784595</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,7 +778,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119683503</v>
+        <v>119683447</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +808,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -841,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481058</v>
+        <v>481045</v>
       </c>
       <c r="R3" t="n">
-        <v>6784561</v>
+        <v>6784589</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119683370</v>
+        <v>119683489</v>
       </c>
       <c r="B4" t="n">
         <v>89252</v>
@@ -947,26 +944,19 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481038</v>
+        <v>481045</v>
       </c>
       <c r="R4" t="n">
-        <v>6784595</v>
+        <v>6784589</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,6 +1007,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1035,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119683489</v>
+        <v>119683440</v>
       </c>
       <c r="B5" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,28 +1038,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1083,7 +1083,7 @@
         <v>6784589</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119683440</v>
+        <v>119683503</v>
       </c>
       <c r="B6" t="n">
         <v>91840</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481045</v>
+        <v>481058</v>
       </c>
       <c r="R6" t="n">
-        <v>6784589</v>
+        <v>6784561</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119706984</v>
+        <v>119706849</v>
       </c>
       <c r="B7" t="n">
-        <v>90067</v>
+        <v>91856</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,32 +1286,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>256703</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1321,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481148</v>
+        <v>481066</v>
       </c>
       <c r="R7" t="n">
-        <v>6784737</v>
+        <v>6784502</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1384,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119706890</v>
+        <v>119706741</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,25 +1392,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1427,7 +1423,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481078</v>
+        <v>481017</v>
       </c>
       <c r="R8" t="n">
         <v>6784518</v>
@@ -1490,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119707034</v>
+        <v>119706918</v>
       </c>
       <c r="B9" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,32 +1498,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1537,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480988</v>
+        <v>481159</v>
       </c>
       <c r="R9" t="n">
-        <v>6784561</v>
+        <v>6784628</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,11 +1565,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>och troligen 2 gamla också</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119706915</v>
+        <v>119706923</v>
       </c>
       <c r="B10" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,21 +1608,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481115</v>
+        <v>481092</v>
       </c>
       <c r="R10" t="n">
-        <v>6784610</v>
+        <v>6784685</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1711,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119706849</v>
+        <v>119706847</v>
       </c>
       <c r="B11" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481066</v>
+        <v>481062</v>
       </c>
       <c r="R11" t="n">
-        <v>6784502</v>
+        <v>6784508</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1817,7 +1804,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119706728</v>
+        <v>119706890</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1860,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480980</v>
+        <v>481078</v>
       </c>
       <c r="R12" t="n">
-        <v>6784536</v>
+        <v>6784518</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1923,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119706885</v>
+        <v>119706842</v>
       </c>
       <c r="B13" t="n">
         <v>91856</v>
@@ -1966,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481077</v>
+        <v>481041</v>
       </c>
       <c r="R13" t="n">
-        <v>6784510</v>
+        <v>6784511</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2029,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119707027</v>
+        <v>119706939</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,32 +2028,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2076,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480985</v>
+        <v>481111</v>
       </c>
       <c r="R14" t="n">
-        <v>6784560</v>
+        <v>6784709</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2139,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119706846</v>
+        <v>119706885</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481066</v>
+        <v>481077</v>
       </c>
       <c r="R15" t="n">
-        <v>6784528</v>
+        <v>6784510</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2245,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119706741</v>
+        <v>119706877</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,25 +2240,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481017</v>
+        <v>481065</v>
       </c>
       <c r="R16" t="n">
-        <v>6784518</v>
+        <v>6784504</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2351,10 +2334,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119706939</v>
+        <v>119706984</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>90067</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,28 +2346,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2394,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481111</v>
+        <v>481148</v>
       </c>
       <c r="R17" t="n">
-        <v>6784709</v>
+        <v>6784737</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2457,10 +2444,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119706842</v>
+        <v>119707034</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2469,28 +2456,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2500,10 +2491,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481041</v>
+        <v>480988</v>
       </c>
       <c r="R18" t="n">
-        <v>6784511</v>
+        <v>6784561</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2536,6 +2527,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>och troligen 2 gamla också</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119706873</v>
+        <v>119707027</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>89252</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,28 +2571,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481067</v>
+        <v>480985</v>
       </c>
       <c r="R19" t="n">
-        <v>6784504</v>
+        <v>6784560</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119706918</v>
+        <v>119706873</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481159</v>
+        <v>481067</v>
       </c>
       <c r="R20" t="n">
-        <v>6784628</v>
+        <v>6784504</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119706877</v>
+        <v>119706870</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>89252</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2787,28 +2787,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2818,7 +2822,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481065</v>
+        <v>481067</v>
       </c>
       <c r="R21" t="n">
         <v>6784504</v>
@@ -2881,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119706870</v>
+        <v>119706915</v>
       </c>
       <c r="B22" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2893,32 +2897,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481067</v>
+        <v>481115</v>
       </c>
       <c r="R22" t="n">
-        <v>6784504</v>
+        <v>6784610</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706923</v>
+        <v>119706846</v>
       </c>
       <c r="B23" t="n">
         <v>78526</v>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481092</v>
+        <v>481066</v>
       </c>
       <c r="R23" t="n">
-        <v>6784685</v>
+        <v>6784528</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706847</v>
+        <v>119706931</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3113,21 +3113,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481062</v>
+        <v>481112</v>
       </c>
       <c r="R24" t="n">
-        <v>6784508</v>
+        <v>6784721</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119706931</v>
+        <v>119706728</v>
       </c>
       <c r="B25" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,21 +3219,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481112</v>
+        <v>480980</v>
       </c>
       <c r="R25" t="n">
-        <v>6784721</v>
+        <v>6784536</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119741905</v>
+        <v>119741440</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,25 +3321,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,7 +3355,7 @@
         <v>6784535</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119741440</v>
+        <v>119741905</v>
       </c>
       <c r="B27" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3433,25 +3433,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
         <v>6784535</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119787935</v>
+        <v>119787807</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3549,34 +3549,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481160</v>
+        <v>481250</v>
       </c>
       <c r="R28" t="n">
-        <v>6784611</v>
+        <v>6784659</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,9 +3606,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3623,19 +3633,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119789001</v>
+        <v>119787665</v>
       </c>
       <c r="B29" t="n">
         <v>91856</v>
@@ -3675,10 +3685,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481138</v>
+        <v>481287</v>
       </c>
       <c r="R29" t="n">
-        <v>6784747</v>
+        <v>6784633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3725,22 +3735,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119787094</v>
+        <v>119789064</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3749,25 +3759,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3777,10 +3787,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481175</v>
+        <v>481010</v>
       </c>
       <c r="R30" t="n">
-        <v>6784516</v>
+        <v>6784679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3839,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119786836</v>
+        <v>119788766</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>78527</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3855,16 +3865,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3879,10 +3889,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481049</v>
+        <v>481176</v>
       </c>
       <c r="R31" t="n">
-        <v>6784514</v>
+        <v>6784737</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3929,22 +3939,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788312</v>
+        <v>119788033</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3957,21 +3967,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3981,10 +3991,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481062</v>
+        <v>481181</v>
       </c>
       <c r="R32" t="n">
-        <v>6784614</v>
+        <v>6784644</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,22 +4041,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119789016</v>
+        <v>119786836</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4055,25 +4065,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4083,10 +4093,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480995</v>
+        <v>481049</v>
       </c>
       <c r="R33" t="n">
-        <v>6784692</v>
+        <v>6784514</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,7 +4155,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119788950</v>
+        <v>119788662</v>
       </c>
       <c r="B34" t="n">
         <v>91840</v>
@@ -4181,14 +4191,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480996</v>
+        <v>481133</v>
       </c>
       <c r="R34" t="n">
-        <v>6784667</v>
+        <v>6784731</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4218,19 +4228,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4245,19 +4245,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119788519</v>
+        <v>119787848</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481087</v>
+        <v>481187</v>
       </c>
       <c r="R35" t="n">
-        <v>6784724</v>
+        <v>6784640</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119786882</v>
+        <v>119788514</v>
       </c>
       <c r="B36" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4371,25 +4371,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481048</v>
+        <v>481088</v>
       </c>
       <c r="R36" t="n">
-        <v>6784513</v>
+        <v>6784614</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119787759</v>
+        <v>119789016</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4473,25 +4473,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481248</v>
+        <v>480995</v>
       </c>
       <c r="R37" t="n">
-        <v>6784628</v>
+        <v>6784692</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119787744</v>
+        <v>119787833</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481267</v>
+        <v>481250</v>
       </c>
       <c r="R38" t="n">
-        <v>6784656</v>
+        <v>6784659</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4675,10 +4675,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119787764</v>
+        <v>119787715</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481252</v>
+        <v>481274</v>
       </c>
       <c r="R39" t="n">
-        <v>6784627</v>
+        <v>6784652</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119787848</v>
+        <v>119789077</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4789,25 +4789,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481187</v>
+        <v>481052</v>
       </c>
       <c r="R40" t="n">
-        <v>6784640</v>
+        <v>6784759</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4867,22 +4867,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119788565</v>
+        <v>119787021</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4891,25 +4891,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481108</v>
+        <v>481048</v>
       </c>
       <c r="R41" t="n">
-        <v>6784708</v>
+        <v>6784513</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4969,22 +4969,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119788482</v>
+        <v>119787028</v>
       </c>
       <c r="B42" t="n">
-        <v>89275</v>
+        <v>91856</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4993,25 +4993,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481092</v>
+        <v>481150</v>
       </c>
       <c r="R42" t="n">
-        <v>6784610</v>
+        <v>6784524</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119792265</v>
+        <v>119788774</v>
       </c>
       <c r="B43" t="n">
-        <v>89239</v>
+        <v>88153</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5095,48 +5095,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6268</v>
+        <v>4962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481044</v>
+        <v>481195</v>
       </c>
       <c r="R43" t="n">
-        <v>6784736</v>
+        <v>6784739</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5163,18 +5156,27 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5193,10 +5195,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119788776</v>
+        <v>119787470</v>
       </c>
       <c r="B44" t="n">
-        <v>91856</v>
+        <v>91821</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5205,25 +5207,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>6055</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5233,10 +5235,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481179</v>
+        <v>481284</v>
       </c>
       <c r="R44" t="n">
-        <v>6784744</v>
+        <v>6784549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5295,10 +5297,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119788033</v>
+        <v>119787002</v>
       </c>
       <c r="B45" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5311,21 +5313,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5335,10 +5337,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481181</v>
+        <v>481114</v>
       </c>
       <c r="R45" t="n">
-        <v>6784644</v>
+        <v>6784523</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5397,10 +5399,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119787115</v>
+        <v>119788574</v>
       </c>
       <c r="B46" t="n">
-        <v>91856</v>
+        <v>8432</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5409,38 +5411,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481178</v>
+        <v>481104</v>
       </c>
       <c r="R46" t="n">
-        <v>6784510</v>
+        <v>6784681</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5470,9 +5477,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5487,22 +5504,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119787167</v>
+        <v>119788519</v>
       </c>
       <c r="B47" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5511,25 +5528,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5539,10 +5556,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481197</v>
+        <v>481087</v>
       </c>
       <c r="R47" t="n">
-        <v>6784509</v>
+        <v>6784724</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5601,10 +5618,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119789064</v>
+        <v>119787935</v>
       </c>
       <c r="B48" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5617,21 +5634,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5641,10 +5658,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481010</v>
+        <v>481160</v>
       </c>
       <c r="R48" t="n">
-        <v>6784679</v>
+        <v>6784611</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5691,22 +5708,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788483</v>
+        <v>119788928</v>
       </c>
       <c r="B49" t="n">
-        <v>89275</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5715,38 +5732,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6286</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481050</v>
+        <v>481138</v>
       </c>
       <c r="R49" t="n">
-        <v>6784604</v>
+        <v>6784747</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5776,19 +5793,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5803,19 +5810,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119788715</v>
+        <v>119786882</v>
       </c>
       <c r="B50" t="n">
         <v>91856</v>
@@ -5851,14 +5858,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481104</v>
+        <v>481048</v>
       </c>
       <c r="R50" t="n">
-        <v>6784681</v>
+        <v>6784513</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5888,19 +5895,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5915,22 +5912,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119787002</v>
+        <v>119789066</v>
       </c>
       <c r="B51" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5943,34 +5940,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481114</v>
+        <v>480996</v>
       </c>
       <c r="R51" t="n">
-        <v>6784523</v>
+        <v>6784667</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6000,9 +5997,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6017,22 +6024,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119787790</v>
+        <v>119787115</v>
       </c>
       <c r="B52" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6045,21 +6052,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6069,10 +6076,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481260</v>
+        <v>481178</v>
       </c>
       <c r="R52" t="n">
-        <v>6784612</v>
+        <v>6784510</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6131,10 +6138,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119788571</v>
+        <v>119788082</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6147,21 +6154,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6171,10 +6178,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481088</v>
+        <v>481144</v>
       </c>
       <c r="R53" t="n">
-        <v>6784614</v>
+        <v>6784602</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6221,22 +6228,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119787021</v>
+        <v>119788715</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6249,34 +6256,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481048</v>
+        <v>481104</v>
       </c>
       <c r="R54" t="n">
-        <v>6784513</v>
+        <v>6784681</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6306,9 +6313,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6323,22 +6340,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119787665</v>
+        <v>119787827</v>
       </c>
       <c r="B55" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6347,25 +6364,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6375,10 +6392,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481287</v>
+        <v>481229</v>
       </c>
       <c r="R55" t="n">
-        <v>6784633</v>
+        <v>6784643</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,10 +6454,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119788574</v>
+        <v>119787744</v>
       </c>
       <c r="B56" t="n">
-        <v>8432</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6449,46 +6466,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481104</v>
+        <v>481267</v>
       </c>
       <c r="R56" t="n">
-        <v>6784681</v>
+        <v>6784656</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6517,7 +6529,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6527,7 +6539,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6554,10 +6566,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119787740</v>
+        <v>119788560</v>
       </c>
       <c r="B57" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6566,25 +6578,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6594,10 +6606,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481276</v>
+        <v>481088</v>
       </c>
       <c r="R57" t="n">
-        <v>6784646</v>
+        <v>6784614</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6870,10 +6882,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119788786</v>
+        <v>119788782</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>91863</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6886,34 +6898,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481176</v>
+        <v>481195</v>
       </c>
       <c r="R60" t="n">
-        <v>6784737</v>
+        <v>6784739</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6943,9 +6964,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6960,22 +6991,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119787825</v>
+        <v>119787167</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6988,34 +7019,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481250</v>
+        <v>481197</v>
       </c>
       <c r="R61" t="n">
-        <v>6784659</v>
+        <v>6784509</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7045,19 +7076,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7072,22 +7093,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119789066</v>
+        <v>119787790</v>
       </c>
       <c r="B62" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7100,34 +7121,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480996</v>
+        <v>481260</v>
       </c>
       <c r="R62" t="n">
-        <v>6784667</v>
+        <v>6784612</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7157,19 +7178,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7184,22 +7195,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119787807</v>
+        <v>119787771</v>
       </c>
       <c r="B63" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7212,34 +7223,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481250</v>
+        <v>481276</v>
       </c>
       <c r="R63" t="n">
-        <v>6784659</v>
+        <v>6784646</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7269,19 +7280,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7296,22 +7297,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119788082</v>
+        <v>119788483</v>
       </c>
       <c r="B64" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7320,38 +7321,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481144</v>
+        <v>481050</v>
       </c>
       <c r="R64" t="n">
-        <v>6784602</v>
+        <v>6784604</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7381,9 +7382,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7398,22 +7409,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119788782</v>
+        <v>119788908</v>
       </c>
       <c r="B65" t="n">
-        <v>91863</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7426,43 +7437,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481195</v>
+        <v>481028</v>
       </c>
       <c r="R65" t="n">
-        <v>6784739</v>
+        <v>6784697</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7492,19 +7494,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7519,22 +7511,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119787544</v>
+        <v>119788846</v>
       </c>
       <c r="B66" t="n">
-        <v>8432</v>
+        <v>91832</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7543,47 +7535,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>4361</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481291</v>
+        <v>481139</v>
       </c>
       <c r="R66" t="n">
-        <v>6784590</v>
+        <v>6784744</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7613,47 +7596,36 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119787827</v>
+        <v>119788565</v>
       </c>
       <c r="B67" t="n">
         <v>91840</v>
@@ -7693,10 +7665,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481229</v>
+        <v>481108</v>
       </c>
       <c r="R67" t="n">
-        <v>6784643</v>
+        <v>6784708</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7755,10 +7727,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119788774</v>
+        <v>119788950</v>
       </c>
       <c r="B68" t="n">
-        <v>88153</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7767,25 +7739,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7795,10 +7767,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>481195</v>
+        <v>480996</v>
       </c>
       <c r="R68" t="n">
-        <v>6784739</v>
+        <v>6784667</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7830,7 +7802,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7840,7 +7812,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7867,10 +7839,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119787028</v>
+        <v>119787681</v>
       </c>
       <c r="B69" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7883,21 +7855,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7907,10 +7879,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481150</v>
+        <v>481294</v>
       </c>
       <c r="R69" t="n">
-        <v>6784524</v>
+        <v>6784626</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7969,10 +7941,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119789105</v>
+        <v>119787774</v>
       </c>
       <c r="B70" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7985,21 +7957,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8009,10 +7981,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481038</v>
+        <v>481250</v>
       </c>
       <c r="R70" t="n">
-        <v>6784721</v>
+        <v>6784627</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8071,10 +8043,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119787774</v>
+        <v>119788312</v>
       </c>
       <c r="B71" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8087,21 +8059,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8083,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481250</v>
+        <v>481062</v>
       </c>
       <c r="R71" t="n">
-        <v>6784627</v>
+        <v>6784614</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,22 +8133,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119788662</v>
+        <v>119789434</v>
       </c>
       <c r="B72" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8185,38 +8157,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481133</v>
+        <v>481002</v>
       </c>
       <c r="R72" t="n">
-        <v>6784731</v>
+        <v>6784693</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8246,9 +8223,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8263,22 +8250,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119788846</v>
+        <v>119788305</v>
       </c>
       <c r="B73" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8291,37 +8278,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481139</v>
+        <v>481083</v>
       </c>
       <c r="R73" t="n">
-        <v>6784744</v>
+        <v>6784643</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8348,9 +8335,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8365,22 +8362,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119789077</v>
+        <v>119787094</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8389,25 +8386,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8417,10 +8414,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481052</v>
+        <v>481175</v>
       </c>
       <c r="R74" t="n">
-        <v>6784759</v>
+        <v>6784516</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8467,22 +8464,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119786992</v>
+        <v>119788550</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>90067</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8495,34 +8492,43 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481048</v>
+        <v>481050</v>
       </c>
       <c r="R75" t="n">
-        <v>6784513</v>
+        <v>6784604</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8552,9 +8558,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8569,22 +8585,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119787139</v>
+        <v>119786992</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8593,35 +8609,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481215</v>
+        <v>481048</v>
       </c>
       <c r="R76" t="n">
         <v>6784513</v>
@@ -8654,19 +8670,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8681,19 +8687,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119788935</v>
+        <v>119788776</v>
       </c>
       <c r="B77" t="n">
         <v>91856</v>
@@ -8733,10 +8739,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>480987</v>
+        <v>481179</v>
       </c>
       <c r="R77" t="n">
-        <v>6784663</v>
+        <v>6784744</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8795,10 +8801,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119787470</v>
+        <v>119788935</v>
       </c>
       <c r="B78" t="n">
-        <v>91821</v>
+        <v>91856</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8807,25 +8813,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6055</v>
+        <v>2059</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8835,10 +8841,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481284</v>
+        <v>480987</v>
       </c>
       <c r="R78" t="n">
-        <v>6784549</v>
+        <v>6784663</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8897,10 +8903,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788104</v>
+        <v>119787759</v>
       </c>
       <c r="B79" t="n">
-        <v>8432</v>
+        <v>79144</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8909,43 +8915,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481122</v>
+        <v>481248</v>
       </c>
       <c r="R79" t="n">
-        <v>6784602</v>
+        <v>6784628</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9004,10 +9005,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119787715</v>
+        <v>119787139</v>
       </c>
       <c r="B80" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9020,34 +9021,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481274</v>
+        <v>481215</v>
       </c>
       <c r="R80" t="n">
-        <v>6784652</v>
+        <v>6784513</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9077,9 +9078,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9094,22 +9105,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119787771</v>
+        <v>119787770</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9122,34 +9133,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481276</v>
+        <v>481267</v>
       </c>
       <c r="R81" t="n">
-        <v>6784646</v>
+        <v>6784656</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9179,9 +9190,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9196,22 +9217,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119788094</v>
+        <v>119788104</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9224,34 +9245,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481132</v>
+        <v>481122</v>
       </c>
       <c r="R82" t="n">
-        <v>6784594</v>
+        <v>6784602</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9298,22 +9324,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119788514</v>
+        <v>119789105</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9322,25 +9348,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9350,10 +9376,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481088</v>
+        <v>481038</v>
       </c>
       <c r="R83" t="n">
-        <v>6784614</v>
+        <v>6784721</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9400,22 +9426,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119787644</v>
+        <v>119789001</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9428,21 +9454,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9452,10 +9478,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481277</v>
+        <v>481138</v>
       </c>
       <c r="R84" t="n">
-        <v>6784621</v>
+        <v>6784747</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9514,10 +9540,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788908</v>
+        <v>119788094</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9526,25 +9552,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9554,10 +9580,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481028</v>
+        <v>481132</v>
       </c>
       <c r="R85" t="n">
-        <v>6784697</v>
+        <v>6784594</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9604,22 +9630,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119789434</v>
+        <v>119787740</v>
       </c>
       <c r="B86" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9628,43 +9654,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481002</v>
+        <v>481276</v>
       </c>
       <c r="R86" t="n">
-        <v>6784693</v>
+        <v>6784646</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9694,19 +9715,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9721,19 +9732,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788928</v>
+        <v>119787644</v>
       </c>
       <c r="B87" t="n">
         <v>78526</v>
@@ -9773,10 +9784,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481138</v>
+        <v>481277</v>
       </c>
       <c r="R87" t="n">
-        <v>6784747</v>
+        <v>6784621</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9835,10 +9846,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119787770</v>
+        <v>119787764</v>
       </c>
       <c r="B88" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9851,34 +9862,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481267</v>
+        <v>481252</v>
       </c>
       <c r="R88" t="n">
-        <v>6784656</v>
+        <v>6784627</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9908,19 +9919,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9935,22 +9936,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119788305</v>
+        <v>119788482</v>
       </c>
       <c r="B89" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9959,41 +9960,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481083</v>
+        <v>481092</v>
       </c>
       <c r="R89" t="n">
-        <v>6784643</v>
+        <v>6784610</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10020,19 +10021,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10047,22 +10038,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119787681</v>
+        <v>119792265</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>89239</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10071,41 +10062,48 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6268</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481294</v>
+        <v>481044</v>
       </c>
       <c r="R90" t="n">
-        <v>6784626</v>
+        <v>6784736</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10143,28 +10141,29 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119788550</v>
+        <v>119787544</v>
       </c>
       <c r="B91" t="n">
-        <v>90067</v>
+        <v>8432</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10177,43 +10176,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>256703</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481050</v>
+        <v>481291</v>
       </c>
       <c r="R91" t="n">
-        <v>6784604</v>
+        <v>6784590</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10245,7 +10244,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10255,7 +10254,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10264,6 +10263,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -2122,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119706885</v>
+        <v>119706877</v>
       </c>
       <c r="B15" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481077</v>
+        <v>481065</v>
       </c>
       <c r="R15" t="n">
-        <v>6784510</v>
+        <v>6784504</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119706877</v>
+        <v>119706885</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481065</v>
+        <v>481077</v>
       </c>
       <c r="R16" t="n">
-        <v>6784504</v>
+        <v>6784510</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119707027</v>
+        <v>119706873</v>
       </c>
       <c r="B19" t="n">
-        <v>89252</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,32 +2571,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2606,10 +2602,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480985</v>
+        <v>481067</v>
       </c>
       <c r="R19" t="n">
-        <v>6784560</v>
+        <v>6784504</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2669,10 +2665,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119706873</v>
+        <v>119707027</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>89252</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2681,28 +2677,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481067</v>
+        <v>480985</v>
       </c>
       <c r="R20" t="n">
-        <v>6784504</v>
+        <v>6784560</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119787807</v>
+        <v>119788766</v>
       </c>
       <c r="B28" t="n">
-        <v>91856</v>
+        <v>78527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3549,34 +3549,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>230405</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481250</v>
+        <v>481176</v>
       </c>
       <c r="R28" t="n">
-        <v>6784659</v>
+        <v>6784737</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,19 +3606,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3633,19 +3623,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119787665</v>
+        <v>119787807</v>
       </c>
       <c r="B29" t="n">
         <v>91856</v>
@@ -3681,14 +3671,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481287</v>
+        <v>481250</v>
       </c>
       <c r="R29" t="n">
-        <v>6784633</v>
+        <v>6784659</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,9 +3708,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,22 +3735,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119789064</v>
+        <v>119787665</v>
       </c>
       <c r="B30" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3763,21 +3763,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481010</v>
+        <v>481287</v>
       </c>
       <c r="R30" t="n">
-        <v>6784679</v>
+        <v>6784633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3849,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788766</v>
+        <v>119789064</v>
       </c>
       <c r="B31" t="n">
-        <v>78527</v>
+        <v>91884</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3865,21 +3865,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230405</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481176</v>
+        <v>481010</v>
       </c>
       <c r="R31" t="n">
-        <v>6784737</v>
+        <v>6784679</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3939,22 +3939,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788033</v>
+        <v>119786836</v>
       </c>
       <c r="B32" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3967,21 +3967,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481181</v>
+        <v>481049</v>
       </c>
       <c r="R32" t="n">
-        <v>6784644</v>
+        <v>6784514</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4053,10 +4053,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119786836</v>
+        <v>119788033</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4069,21 +4069,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481049</v>
+        <v>481181</v>
       </c>
       <c r="R33" t="n">
-        <v>6784514</v>
+        <v>6784644</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -8597,10 +8597,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119786992</v>
+        <v>119787759</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8609,25 +8609,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481048</v>
+        <v>481248</v>
       </c>
       <c r="R76" t="n">
-        <v>6784513</v>
+        <v>6784628</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8687,22 +8687,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119788776</v>
+        <v>119787139</v>
       </c>
       <c r="B77" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8715,34 +8715,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481179</v>
+        <v>481215</v>
       </c>
       <c r="R77" t="n">
-        <v>6784744</v>
+        <v>6784513</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8772,9 +8772,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8789,22 +8799,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119788935</v>
+        <v>119786992</v>
       </c>
       <c r="B78" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8813,25 +8823,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8841,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480987</v>
+        <v>481048</v>
       </c>
       <c r="R78" t="n">
-        <v>6784663</v>
+        <v>6784513</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8891,22 +8901,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119787759</v>
+        <v>119788776</v>
       </c>
       <c r="B79" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8919,21 +8929,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8943,10 +8953,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481248</v>
+        <v>481179</v>
       </c>
       <c r="R79" t="n">
-        <v>6784628</v>
+        <v>6784744</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9005,10 +9015,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119787139</v>
+        <v>119788935</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9021,34 +9031,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481215</v>
+        <v>480987</v>
       </c>
       <c r="R80" t="n">
-        <v>6784513</v>
+        <v>6784663</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9078,19 +9088,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,12 +9105,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119683370</v>
+        <v>119683503</v>
       </c>
       <c r="B2" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,16 +718,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481038</v>
+        <v>481058</v>
       </c>
       <c r="R2" t="n">
-        <v>6784595</v>
+        <v>6784561</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +780,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119683447</v>
+        <v>119683489</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -873,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119683489</v>
+        <v>119683447</v>
       </c>
       <c r="B4" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -988,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119683440</v>
+        <v>119683370</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,30 +1041,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1069,21 +1072,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481045</v>
+        <v>481038</v>
       </c>
       <c r="R5" t="n">
-        <v>6784589</v>
+        <v>6784595</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1132,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119683503</v>
+        <v>119683440</v>
       </c>
       <c r="B6" t="n">
         <v>91840</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481058</v>
+        <v>481045</v>
       </c>
       <c r="R6" t="n">
-        <v>6784561</v>
+        <v>6784589</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119706849</v>
+        <v>119707034</v>
       </c>
       <c r="B7" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,28 +1286,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1317,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481066</v>
+        <v>480988</v>
       </c>
       <c r="R7" t="n">
-        <v>6784502</v>
+        <v>6784561</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,6 +1357,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>och troligen 2 gamla också</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119706741</v>
+        <v>119706846</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,25 +1401,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481017</v>
+        <v>481066</v>
       </c>
       <c r="R8" t="n">
-        <v>6784518</v>
+        <v>6784528</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1486,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119706918</v>
+        <v>119706741</v>
       </c>
       <c r="B9" t="n">
         <v>91840</v>
@@ -1529,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481159</v>
+        <v>481017</v>
       </c>
       <c r="R9" t="n">
-        <v>6784628</v>
+        <v>6784518</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1804,7 +1813,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119706890</v>
+        <v>119706877</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1847,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481078</v>
+        <v>481065</v>
       </c>
       <c r="R12" t="n">
-        <v>6784518</v>
+        <v>6784504</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1910,10 +1919,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119706842</v>
+        <v>119707027</v>
       </c>
       <c r="B13" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,28 +1931,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1953,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481041</v>
+        <v>480985</v>
       </c>
       <c r="R13" t="n">
-        <v>6784511</v>
+        <v>6784560</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2016,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119706939</v>
+        <v>119706931</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,21 +2045,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481111</v>
+        <v>481112</v>
       </c>
       <c r="R14" t="n">
-        <v>6784709</v>
+        <v>6784721</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2122,7 +2135,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119706877</v>
+        <v>119706939</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2165,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481065</v>
+        <v>481111</v>
       </c>
       <c r="R15" t="n">
-        <v>6784504</v>
+        <v>6784709</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2241,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119706885</v>
+        <v>119706915</v>
       </c>
       <c r="B16" t="n">
         <v>91856</v>
@@ -2271,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481077</v>
+        <v>481115</v>
       </c>
       <c r="R16" t="n">
-        <v>6784510</v>
+        <v>6784610</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2334,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119706984</v>
+        <v>119706890</v>
       </c>
       <c r="B17" t="n">
-        <v>90067</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,32 +2359,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2381,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481148</v>
+        <v>481078</v>
       </c>
       <c r="R17" t="n">
-        <v>6784737</v>
+        <v>6784518</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2444,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119707034</v>
+        <v>119706842</v>
       </c>
       <c r="B18" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2456,32 +2465,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2491,10 +2496,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480988</v>
+        <v>481041</v>
       </c>
       <c r="R18" t="n">
-        <v>6784561</v>
+        <v>6784511</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2527,11 +2532,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>och troligen 2 gamla också</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2665,7 +2665,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119707027</v>
+        <v>119706870</v>
       </c>
       <c r="B20" t="n">
         <v>89252</v>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480985</v>
+        <v>481067</v>
       </c>
       <c r="R20" t="n">
-        <v>6784560</v>
+        <v>6784504</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119706870</v>
+        <v>119706885</v>
       </c>
       <c r="B21" t="n">
-        <v>89252</v>
+        <v>91856</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2787,32 +2787,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2822,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481067</v>
+        <v>481077</v>
       </c>
       <c r="R21" t="n">
-        <v>6784504</v>
+        <v>6784510</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2885,10 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119706915</v>
+        <v>119706728</v>
       </c>
       <c r="B22" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2901,21 +2897,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2928,10 +2924,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481115</v>
+        <v>480980</v>
       </c>
       <c r="R22" t="n">
-        <v>6784610</v>
+        <v>6784536</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2991,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706846</v>
+        <v>119706984</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>90067</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3003,28 +2999,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481066</v>
+        <v>481148</v>
       </c>
       <c r="R23" t="n">
-        <v>6784528</v>
+        <v>6784737</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706931</v>
+        <v>119706918</v>
       </c>
       <c r="B24" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3109,25 +3109,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481112</v>
+        <v>481159</v>
       </c>
       <c r="R24" t="n">
-        <v>6784721</v>
+        <v>6784628</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119706728</v>
+        <v>119706849</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3219,21 +3219,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480980</v>
+        <v>481066</v>
       </c>
       <c r="R25" t="n">
-        <v>6784536</v>
+        <v>6784502</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788766</v>
+        <v>119788935</v>
       </c>
       <c r="B28" t="n">
-        <v>78527</v>
+        <v>91856</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230405</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481176</v>
+        <v>480987</v>
       </c>
       <c r="R28" t="n">
-        <v>6784737</v>
+        <v>6784663</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,19 +3623,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119787807</v>
+        <v>119787115</v>
       </c>
       <c r="B29" t="n">
         <v>91856</v>
@@ -3671,14 +3671,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481250</v>
+        <v>481178</v>
       </c>
       <c r="R29" t="n">
-        <v>6784659</v>
+        <v>6784510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,19 +3708,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3735,22 +3725,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119787665</v>
+        <v>119787002</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
+        <v>78171</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3763,21 +3753,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3787,10 +3777,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481287</v>
+        <v>481114</v>
       </c>
       <c r="R30" t="n">
-        <v>6784633</v>
+        <v>6784523</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3849,10 +3839,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119789064</v>
+        <v>119788908</v>
       </c>
       <c r="B31" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3865,21 +3855,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3889,10 +3879,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481010</v>
+        <v>481028</v>
       </c>
       <c r="R31" t="n">
-        <v>6784679</v>
+        <v>6784697</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3951,10 +3941,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119786836</v>
+        <v>119788662</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3963,25 +3953,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3991,10 +3981,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481049</v>
+        <v>481133</v>
       </c>
       <c r="R32" t="n">
-        <v>6784514</v>
+        <v>6784731</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4053,10 +4043,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119788033</v>
+        <v>119787774</v>
       </c>
       <c r="B33" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4069,21 +4059,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4093,10 +4083,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481181</v>
+        <v>481250</v>
       </c>
       <c r="R33" t="n">
-        <v>6784644</v>
+        <v>6784627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4155,10 +4145,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119788662</v>
+        <v>119788550</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>90067</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4171,34 +4161,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481133</v>
+        <v>481050</v>
       </c>
       <c r="R34" t="n">
-        <v>6784731</v>
+        <v>6784604</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4228,9 +4227,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4245,22 +4254,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119787848</v>
+        <v>119787167</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4269,25 +4278,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4297,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481187</v>
+        <v>481197</v>
       </c>
       <c r="R35" t="n">
-        <v>6784640</v>
+        <v>6784509</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,10 +4368,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119788514</v>
+        <v>119787807</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4371,38 +4380,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481088</v>
+        <v>481250</v>
       </c>
       <c r="R36" t="n">
-        <v>6784614</v>
+        <v>6784659</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4432,9 +4441,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4449,22 +4468,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119789016</v>
+        <v>119787759</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4473,25 +4492,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4501,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480995</v>
+        <v>481248</v>
       </c>
       <c r="R37" t="n">
-        <v>6784692</v>
+        <v>6784628</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4563,7 +4582,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119787833</v>
+        <v>119787135</v>
       </c>
       <c r="B38" t="n">
         <v>78526</v>
@@ -4599,14 +4618,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481250</v>
+        <v>481048</v>
       </c>
       <c r="R38" t="n">
-        <v>6784659</v>
+        <v>6784513</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4636,19 +4655,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4663,22 +4672,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119787715</v>
+        <v>119788928</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4691,21 +4700,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4715,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481274</v>
+        <v>481138</v>
       </c>
       <c r="R39" t="n">
-        <v>6784652</v>
+        <v>6784747</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4765,22 +4774,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119789077</v>
+        <v>119788782</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>91863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4793,34 +4802,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481052</v>
+        <v>481195</v>
       </c>
       <c r="R40" t="n">
-        <v>6784759</v>
+        <v>6784739</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4850,9 +4868,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,19 +4895,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119787021</v>
+        <v>119787644</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4919,10 +4947,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481048</v>
+        <v>481277</v>
       </c>
       <c r="R41" t="n">
-        <v>6784513</v>
+        <v>6784621</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4981,10 +5009,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119787028</v>
+        <v>119788514</v>
       </c>
       <c r="B42" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4993,25 +5021,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5021,10 +5049,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481150</v>
+        <v>481088</v>
       </c>
       <c r="R42" t="n">
-        <v>6784524</v>
+        <v>6784614</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5071,22 +5099,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119788774</v>
+        <v>119788519</v>
       </c>
       <c r="B43" t="n">
-        <v>88153</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5095,38 +5123,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481195</v>
+        <v>481087</v>
       </c>
       <c r="R43" t="n">
-        <v>6784739</v>
+        <v>6784724</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5156,19 +5184,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5183,22 +5201,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119787470</v>
+        <v>119786882</v>
       </c>
       <c r="B44" t="n">
-        <v>91821</v>
+        <v>91856</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5207,25 +5225,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6055</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5235,10 +5253,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481284</v>
+        <v>481048</v>
       </c>
       <c r="R44" t="n">
-        <v>6784549</v>
+        <v>6784513</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5285,22 +5303,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119787002</v>
+        <v>119789064</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5313,21 +5331,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5337,10 +5355,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481114</v>
+        <v>481010</v>
       </c>
       <c r="R45" t="n">
-        <v>6784523</v>
+        <v>6784679</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5399,10 +5417,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788574</v>
+        <v>119786836</v>
       </c>
       <c r="B46" t="n">
-        <v>8432</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5411,43 +5429,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481104</v>
+        <v>481049</v>
       </c>
       <c r="R46" t="n">
-        <v>6784681</v>
+        <v>6784514</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5477,19 +5490,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5504,19 +5507,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119788519</v>
+        <v>119787740</v>
       </c>
       <c r="B47" t="n">
         <v>91840</v>
@@ -5556,10 +5559,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481087</v>
+        <v>481276</v>
       </c>
       <c r="R47" t="n">
-        <v>6784724</v>
+        <v>6784646</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5606,19 +5609,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119787935</v>
+        <v>119788786</v>
       </c>
       <c r="B48" t="n">
         <v>78526</v>
@@ -5658,10 +5661,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481160</v>
+        <v>481176</v>
       </c>
       <c r="R48" t="n">
-        <v>6784611</v>
+        <v>6784737</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5720,7 +5723,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788928</v>
+        <v>119787744</v>
       </c>
       <c r="B49" t="n">
         <v>78526</v>
@@ -5756,17 +5759,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481138</v>
+        <v>481267</v>
       </c>
       <c r="R49" t="n">
-        <v>6784747</v>
+        <v>6784656</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5793,9 +5796,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5810,22 +5823,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119786882</v>
+        <v>119788483</v>
       </c>
       <c r="B50" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5834,38 +5847,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481048</v>
+        <v>481050</v>
       </c>
       <c r="R50" t="n">
-        <v>6784513</v>
+        <v>6784604</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5895,9 +5908,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5912,22 +5935,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119789066</v>
+        <v>119787771</v>
       </c>
       <c r="B51" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5940,34 +5963,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480996</v>
+        <v>481276</v>
       </c>
       <c r="R51" t="n">
-        <v>6784667</v>
+        <v>6784646</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5997,19 +6020,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6024,22 +6037,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119787115</v>
+        <v>119787764</v>
       </c>
       <c r="B52" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6052,21 +6065,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6076,10 +6089,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481178</v>
+        <v>481252</v>
       </c>
       <c r="R52" t="n">
-        <v>6784510</v>
+        <v>6784627</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6138,10 +6151,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119788082</v>
+        <v>119788571</v>
       </c>
       <c r="B53" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6154,21 +6167,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6178,10 +6191,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481144</v>
+        <v>481088</v>
       </c>
       <c r="R53" t="n">
-        <v>6784602</v>
+        <v>6784614</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6228,19 +6241,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119788715</v>
+        <v>119789066</v>
       </c>
       <c r="B54" t="n">
         <v>91856</v>
@@ -6280,10 +6293,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481104</v>
+        <v>480996</v>
       </c>
       <c r="R54" t="n">
-        <v>6784681</v>
+        <v>6784667</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6315,7 +6328,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6325,7 +6338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6352,10 +6365,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119787827</v>
+        <v>119787715</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6364,25 +6377,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6392,10 +6405,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481229</v>
+        <v>481274</v>
       </c>
       <c r="R55" t="n">
-        <v>6784643</v>
+        <v>6784652</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6454,10 +6467,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119787744</v>
+        <v>119788094</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6466,41 +6479,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481267</v>
+        <v>481132</v>
       </c>
       <c r="R56" t="n">
-        <v>6784656</v>
+        <v>6784594</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6527,19 +6540,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6554,19 +6557,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119788560</v>
+        <v>119789077</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -6606,10 +6609,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481088</v>
+        <v>481052</v>
       </c>
       <c r="R57" t="n">
-        <v>6784614</v>
+        <v>6784759</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6668,10 +6671,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119788851</v>
+        <v>119788715</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6680,25 +6683,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6708,10 +6711,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481136</v>
+        <v>481104</v>
       </c>
       <c r="R58" t="n">
-        <v>6784750</v>
+        <v>6784681</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6743,7 +6746,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6756,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6780,10 +6783,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119789074</v>
+        <v>119789105</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6792,25 +6795,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6820,10 +6823,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481031</v>
+        <v>481038</v>
       </c>
       <c r="R59" t="n">
-        <v>6784712</v>
+        <v>6784721</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6882,10 +6885,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119788782</v>
+        <v>119788305</v>
       </c>
       <c r="B60" t="n">
-        <v>91863</v>
+        <v>91884</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6898,46 +6901,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481195</v>
+        <v>481083</v>
       </c>
       <c r="R60" t="n">
-        <v>6784739</v>
+        <v>6784643</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6966,7 +6960,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6976,7 +6970,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7003,10 +6997,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119787167</v>
+        <v>119788846</v>
       </c>
       <c r="B61" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7019,21 +7013,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7043,10 +7037,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481197</v>
+        <v>481139</v>
       </c>
       <c r="R61" t="n">
-        <v>6784509</v>
+        <v>6784744</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7105,10 +7099,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119787790</v>
+        <v>119789434</v>
       </c>
       <c r="B62" t="n">
-        <v>91834</v>
+        <v>57463</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7121,34 +7115,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481260</v>
+        <v>481002</v>
       </c>
       <c r="R62" t="n">
-        <v>6784612</v>
+        <v>6784693</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7178,9 +7177,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7195,19 +7204,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119787771</v>
+        <v>119787833</v>
       </c>
       <c r="B63" t="n">
         <v>78526</v>
@@ -7243,14 +7252,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481276</v>
+        <v>481250</v>
       </c>
       <c r="R63" t="n">
-        <v>6784646</v>
+        <v>6784659</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7280,9 +7289,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7297,22 +7316,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119788483</v>
+        <v>119792265</v>
       </c>
       <c r="B64" t="n">
-        <v>89275</v>
+        <v>89239</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7321,41 +7340,48 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>6268</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481050</v>
+        <v>481044</v>
       </c>
       <c r="R64" t="n">
-        <v>6784604</v>
+        <v>6784736</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7382,27 +7408,18 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7421,10 +7438,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119788908</v>
+        <v>119788565</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7433,25 +7450,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7461,10 +7478,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481028</v>
+        <v>481108</v>
       </c>
       <c r="R65" t="n">
-        <v>6784697</v>
+        <v>6784708</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7523,10 +7540,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119788846</v>
+        <v>119789001</v>
       </c>
       <c r="B66" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7539,21 +7556,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7563,10 +7580,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481139</v>
+        <v>481138</v>
       </c>
       <c r="R66" t="n">
-        <v>6784744</v>
+        <v>6784747</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7613,22 +7630,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119788565</v>
+        <v>119788033</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7637,25 +7654,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7665,10 +7682,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481108</v>
+        <v>481181</v>
       </c>
       <c r="R67" t="n">
-        <v>6784708</v>
+        <v>6784644</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7727,7 +7744,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119788950</v>
+        <v>119789016</v>
       </c>
       <c r="B68" t="n">
         <v>91840</v>
@@ -7763,14 +7780,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480996</v>
+        <v>480995</v>
       </c>
       <c r="R68" t="n">
-        <v>6784667</v>
+        <v>6784692</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7800,19 +7817,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7827,22 +7834,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119787681</v>
+        <v>119789074</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7851,25 +7858,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7879,10 +7886,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481294</v>
+        <v>481031</v>
       </c>
       <c r="R69" t="n">
-        <v>6784626</v>
+        <v>6784712</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7941,10 +7948,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119787774</v>
+        <v>119788851</v>
       </c>
       <c r="B70" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7953,38 +7960,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481250</v>
+        <v>481136</v>
       </c>
       <c r="R70" t="n">
-        <v>6784627</v>
+        <v>6784750</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8014,9 +8021,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8031,22 +8048,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119788312</v>
+        <v>119788774</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>88153</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8059,34 +8076,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>4962</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481062</v>
+        <v>481195</v>
       </c>
       <c r="R71" t="n">
-        <v>6784614</v>
+        <v>6784739</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8116,9 +8133,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8133,22 +8160,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119789434</v>
+        <v>119788574</v>
       </c>
       <c r="B72" t="n">
-        <v>57463</v>
+        <v>8432</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8157,31 +8184,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8190,10 +8217,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481002</v>
+        <v>481104</v>
       </c>
       <c r="R72" t="n">
-        <v>6784693</v>
+        <v>6784681</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8225,7 +8252,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8235,7 +8262,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8262,10 +8289,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119788305</v>
+        <v>119787827</v>
       </c>
       <c r="B73" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8274,41 +8301,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481083</v>
+        <v>481229</v>
       </c>
       <c r="R73" t="n">
         <v>6784643</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8335,19 +8362,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8362,22 +8379,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119787094</v>
+        <v>119787935</v>
       </c>
       <c r="B74" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8386,25 +8403,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8414,10 +8431,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481175</v>
+        <v>481160</v>
       </c>
       <c r="R74" t="n">
-        <v>6784516</v>
+        <v>6784611</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8464,22 +8481,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119788550</v>
+        <v>119787139</v>
       </c>
       <c r="B75" t="n">
-        <v>90067</v>
+        <v>78526</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8488,47 +8505,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481050</v>
+        <v>481215</v>
       </c>
       <c r="R75" t="n">
-        <v>6784604</v>
+        <v>6784513</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8560,7 +8568,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8570,7 +8578,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8597,10 +8605,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119787759</v>
+        <v>119788482</v>
       </c>
       <c r="B76" t="n">
-        <v>79144</v>
+        <v>89275</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8609,25 +8617,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8645,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481248</v>
+        <v>481092</v>
       </c>
       <c r="R76" t="n">
-        <v>6784628</v>
+        <v>6784610</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8699,10 +8707,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119787139</v>
+        <v>119788104</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>8432</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8711,38 +8719,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481215</v>
+        <v>481122</v>
       </c>
       <c r="R77" t="n">
-        <v>6784513</v>
+        <v>6784602</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8772,19 +8785,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8799,22 +8802,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119786992</v>
+        <v>119787770</v>
       </c>
       <c r="B78" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8823,38 +8826,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481048</v>
+        <v>481267</v>
       </c>
       <c r="R78" t="n">
-        <v>6784513</v>
+        <v>6784656</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8884,9 +8887,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8901,19 +8914,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788776</v>
+        <v>119787028</v>
       </c>
       <c r="B79" t="n">
         <v>91856</v>
@@ -8953,10 +8966,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481179</v>
+        <v>481150</v>
       </c>
       <c r="R79" t="n">
-        <v>6784744</v>
+        <v>6784524</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9015,10 +9028,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119788935</v>
+        <v>119788312</v>
       </c>
       <c r="B80" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9031,21 +9044,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9055,10 +9068,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480987</v>
+        <v>481062</v>
       </c>
       <c r="R80" t="n">
-        <v>6784663</v>
+        <v>6784614</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9105,22 +9118,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119787770</v>
+        <v>119787681</v>
       </c>
       <c r="B81" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9133,34 +9146,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481267</v>
+        <v>481294</v>
       </c>
       <c r="R81" t="n">
-        <v>6784656</v>
+        <v>6784626</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9190,19 +9203,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9217,22 +9220,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119788104</v>
+        <v>119787848</v>
       </c>
       <c r="B82" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9245,39 +9248,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481122</v>
+        <v>481187</v>
       </c>
       <c r="R82" t="n">
-        <v>6784602</v>
+        <v>6784640</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9336,10 +9334,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119789105</v>
+        <v>119786992</v>
       </c>
       <c r="B83" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9348,25 +9346,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9376,10 +9374,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481038</v>
+        <v>481048</v>
       </c>
       <c r="R83" t="n">
-        <v>6784721</v>
+        <v>6784513</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9426,22 +9424,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119789001</v>
+        <v>119787544</v>
       </c>
       <c r="B84" t="n">
-        <v>91856</v>
+        <v>8432</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9450,38 +9448,47 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2059</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481138</v>
+        <v>481291</v>
       </c>
       <c r="R84" t="n">
-        <v>6784747</v>
+        <v>6784590</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9511,39 +9518,50 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788094</v>
+        <v>119787470</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>91821</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9552,25 +9570,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9580,10 +9598,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481132</v>
+        <v>481284</v>
       </c>
       <c r="R85" t="n">
-        <v>6784594</v>
+        <v>6784549</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9630,19 +9648,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119787740</v>
+        <v>119788950</v>
       </c>
       <c r="B86" t="n">
         <v>91840</v>
@@ -9678,14 +9696,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481276</v>
+        <v>480996</v>
       </c>
       <c r="R86" t="n">
-        <v>6784646</v>
+        <v>6784667</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9715,9 +9733,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9732,22 +9760,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119787644</v>
+        <v>119788776</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9760,21 +9788,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9784,10 +9812,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481277</v>
+        <v>481179</v>
       </c>
       <c r="R87" t="n">
-        <v>6784621</v>
+        <v>6784744</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9834,22 +9862,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119787764</v>
+        <v>119787665</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9862,21 +9890,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9886,10 +9914,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481252</v>
+        <v>481287</v>
       </c>
       <c r="R88" t="n">
-        <v>6784627</v>
+        <v>6784633</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9948,10 +9976,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119788482</v>
+        <v>119787790</v>
       </c>
       <c r="B89" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9960,25 +9988,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9988,10 +10016,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481092</v>
+        <v>481260</v>
       </c>
       <c r="R89" t="n">
-        <v>6784610</v>
+        <v>6784612</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10050,10 +10078,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119792265</v>
+        <v>119788082</v>
       </c>
       <c r="B90" t="n">
-        <v>89239</v>
+        <v>91856</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10062,48 +10090,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6268</v>
+        <v>2059</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481044</v>
+        <v>481144</v>
       </c>
       <c r="R90" t="n">
-        <v>6784736</v>
+        <v>6784602</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10141,29 +10162,28 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119787544</v>
+        <v>119787094</v>
       </c>
       <c r="B91" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10176,43 +10196,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481291</v>
+        <v>481175</v>
       </c>
       <c r="R91" t="n">
-        <v>6784590</v>
+        <v>6784516</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10242,40 +10253,29 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -2775,10 +2775,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119706885</v>
+        <v>119706728</v>
       </c>
       <c r="B21" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481077</v>
+        <v>480980</v>
       </c>
       <c r="R21" t="n">
-        <v>6784510</v>
+        <v>6784536</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119706728</v>
+        <v>119706984</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>90067</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2893,28 +2893,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2924,10 +2928,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480980</v>
+        <v>481148</v>
       </c>
       <c r="R22" t="n">
-        <v>6784536</v>
+        <v>6784737</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2987,10 +2991,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706984</v>
+        <v>119706885</v>
       </c>
       <c r="B23" t="n">
-        <v>90067</v>
+        <v>91856</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2999,32 +3003,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256703</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481148</v>
+        <v>481077</v>
       </c>
       <c r="R23" t="n">
-        <v>6784737</v>
+        <v>6784510</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -5947,10 +5947,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119787771</v>
+        <v>119789066</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5963,34 +5963,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481276</v>
+        <v>480996</v>
       </c>
       <c r="R51" t="n">
-        <v>6784646</v>
+        <v>6784667</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6020,9 +6020,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6037,22 +6047,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119787764</v>
+        <v>119787715</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6065,21 +6075,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6089,10 +6099,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481252</v>
+        <v>481274</v>
       </c>
       <c r="R52" t="n">
-        <v>6784627</v>
+        <v>6784652</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6151,7 +6161,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119788571</v>
+        <v>119787771</v>
       </c>
       <c r="B53" t="n">
         <v>78526</v>
@@ -6191,10 +6201,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481088</v>
+        <v>481276</v>
       </c>
       <c r="R53" t="n">
-        <v>6784614</v>
+        <v>6784646</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6253,10 +6263,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119789066</v>
+        <v>119787764</v>
       </c>
       <c r="B54" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6269,34 +6279,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480996</v>
+        <v>481252</v>
       </c>
       <c r="R54" t="n">
-        <v>6784667</v>
+        <v>6784627</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6326,19 +6336,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6353,22 +6353,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119787715</v>
+        <v>119788571</v>
       </c>
       <c r="B55" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6381,21 +6381,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6405,10 +6405,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481274</v>
+        <v>481088</v>
       </c>
       <c r="R55" t="n">
-        <v>6784652</v>
+        <v>6784614</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6455,12 +6455,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6569,10 +6569,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119789077</v>
+        <v>119788715</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6585,34 +6585,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481052</v>
+        <v>481104</v>
       </c>
       <c r="R57" t="n">
-        <v>6784759</v>
+        <v>6784681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6642,9 +6642,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6659,22 +6669,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119788715</v>
+        <v>119789077</v>
       </c>
       <c r="B58" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6687,34 +6697,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481104</v>
+        <v>481052</v>
       </c>
       <c r="R58" t="n">
-        <v>6784681</v>
+        <v>6784759</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,19 +6754,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6771,12 +6771,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7216,10 +7216,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119787833</v>
+        <v>119789001</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7232,34 +7232,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481250</v>
+        <v>481138</v>
       </c>
       <c r="R63" t="n">
-        <v>6784659</v>
+        <v>6784747</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7289,19 +7289,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7316,22 +7306,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119792265</v>
+        <v>119787833</v>
       </c>
       <c r="B64" t="n">
-        <v>89239</v>
+        <v>78526</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7340,48 +7330,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6268</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481044</v>
+        <v>481250</v>
       </c>
       <c r="R64" t="n">
-        <v>6784736</v>
+        <v>6784659</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7408,18 +7391,27 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7438,10 +7430,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119788565</v>
+        <v>119792265</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>89239</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7454,37 +7446,44 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6268</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481108</v>
+        <v>481044</v>
       </c>
       <c r="R65" t="n">
-        <v>6784708</v>
+        <v>6784736</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7522,28 +7521,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119789001</v>
+        <v>119788565</v>
       </c>
       <c r="B66" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7552,25 +7552,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7580,10 +7580,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481138</v>
+        <v>481108</v>
       </c>
       <c r="R66" t="n">
-        <v>6784747</v>
+        <v>6784708</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7630,12 +7630,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119787544</v>
+        <v>119787470</v>
       </c>
       <c r="B84" t="n">
-        <v>8432</v>
+        <v>91821</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9448,47 +9448,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6055</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481291</v>
+        <v>481284</v>
       </c>
       <c r="R84" t="n">
-        <v>6784590</v>
+        <v>6784549</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9518,50 +9509,39 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119787470</v>
+        <v>119788950</v>
       </c>
       <c r="B85" t="n">
-        <v>91821</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9570,38 +9550,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481284</v>
+        <v>480996</v>
       </c>
       <c r="R85" t="n">
-        <v>6784549</v>
+        <v>6784667</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9631,9 +9611,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9648,22 +9638,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788950</v>
+        <v>119787544</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9676,34 +9666,43 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>480996</v>
+        <v>481291</v>
       </c>
       <c r="R86" t="n">
-        <v>6784667</v>
+        <v>6784590</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9735,7 +9734,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9745,7 +9744,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9754,6 +9753,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119683503</v>
+        <v>119683440</v>
       </c>
       <c r="B2" t="n">
         <v>91840</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481058</v>
+        <v>481045</v>
       </c>
       <c r="R2" t="n">
-        <v>6784561</v>
+        <v>6784589</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119683489</v>
+        <v>119683370</v>
       </c>
       <c r="B3" t="n">
         <v>89252</v>
@@ -832,19 +832,26 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481045</v>
+        <v>481038</v>
       </c>
       <c r="R3" t="n">
-        <v>6784589</v>
+        <v>6784595</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +902,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1029,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119683370</v>
+        <v>119683489</v>
       </c>
       <c r="B5" t="n">
         <v>89252</v>
@@ -1062,26 +1068,19 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481038</v>
+        <v>481045</v>
       </c>
       <c r="R5" t="n">
-        <v>6784595</v>
+        <v>6784589</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1131,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119683440</v>
+        <v>119683503</v>
       </c>
       <c r="B6" t="n">
         <v>91840</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481045</v>
+        <v>481058</v>
       </c>
       <c r="R6" t="n">
-        <v>6784589</v>
+        <v>6784561</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119706846</v>
+        <v>119706915</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481066</v>
+        <v>481115</v>
       </c>
       <c r="R8" t="n">
-        <v>6784528</v>
+        <v>6784610</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119706741</v>
+        <v>119706846</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,25 +1507,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481017</v>
+        <v>481066</v>
       </c>
       <c r="R9" t="n">
-        <v>6784518</v>
+        <v>6784528</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119706923</v>
+        <v>119706842</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,21 +1617,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481092</v>
+        <v>481041</v>
       </c>
       <c r="R10" t="n">
-        <v>6784685</v>
+        <v>6784511</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1707,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119706847</v>
+        <v>119706939</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481062</v>
+        <v>481111</v>
       </c>
       <c r="R11" t="n">
-        <v>6784508</v>
+        <v>6784709</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119706877</v>
+        <v>119706849</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481065</v>
+        <v>481066</v>
       </c>
       <c r="R12" t="n">
-        <v>6784504</v>
+        <v>6784502</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119707027</v>
+        <v>119706890</v>
       </c>
       <c r="B13" t="n">
-        <v>89252</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,32 +1931,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1966,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480985</v>
+        <v>481078</v>
       </c>
       <c r="R13" t="n">
-        <v>6784560</v>
+        <v>6784518</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2029,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119706931</v>
+        <v>119706984</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>90067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,28 +2037,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481112</v>
+        <v>481148</v>
       </c>
       <c r="R14" t="n">
-        <v>6784721</v>
+        <v>6784737</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119706939</v>
+        <v>119706847</v>
       </c>
       <c r="B15" t="n">
         <v>78526</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481111</v>
+        <v>481062</v>
       </c>
       <c r="R15" t="n">
-        <v>6784709</v>
+        <v>6784508</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119706915</v>
+        <v>119707027</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,28 +2253,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2284,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481115</v>
+        <v>480985</v>
       </c>
       <c r="R16" t="n">
-        <v>6784610</v>
+        <v>6784560</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2347,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119706890</v>
+        <v>119706885</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,21 +2367,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481078</v>
+        <v>481077</v>
       </c>
       <c r="R17" t="n">
-        <v>6784518</v>
+        <v>6784510</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2453,10 +2457,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119706842</v>
+        <v>119706877</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2469,21 +2473,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2496,10 +2500,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481041</v>
+        <v>481065</v>
       </c>
       <c r="R18" t="n">
-        <v>6784511</v>
+        <v>6784504</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2559,7 +2563,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119706873</v>
+        <v>119706728</v>
       </c>
       <c r="B19" t="n">
         <v>78526</v>
@@ -2602,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481067</v>
+        <v>480980</v>
       </c>
       <c r="R19" t="n">
-        <v>6784504</v>
+        <v>6784536</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2665,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119706870</v>
+        <v>119706918</v>
       </c>
       <c r="B20" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,32 +2681,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481067</v>
+        <v>481159</v>
       </c>
       <c r="R20" t="n">
-        <v>6784504</v>
+        <v>6784628</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2775,7 +2775,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119706728</v>
+        <v>119706873</v>
       </c>
       <c r="B21" t="n">
         <v>78526</v>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480980</v>
+        <v>481067</v>
       </c>
       <c r="R21" t="n">
-        <v>6784536</v>
+        <v>6784504</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119706984</v>
+        <v>119706923</v>
       </c>
       <c r="B22" t="n">
-        <v>90067</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2893,32 +2893,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>256703</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2928,10 +2924,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>481148</v>
+        <v>481092</v>
       </c>
       <c r="R22" t="n">
-        <v>6784737</v>
+        <v>6784685</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2991,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706885</v>
+        <v>119706741</v>
       </c>
       <c r="B23" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3003,25 +2999,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3034,10 +3030,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481077</v>
+        <v>481017</v>
       </c>
       <c r="R23" t="n">
-        <v>6784510</v>
+        <v>6784518</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3097,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706918</v>
+        <v>119706870</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3109,28 +3105,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481159</v>
+        <v>481067</v>
       </c>
       <c r="R24" t="n">
-        <v>6784628</v>
+        <v>6784504</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119706849</v>
+        <v>119706931</v>
       </c>
       <c r="B25" t="n">
         <v>91856</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>481066</v>
+        <v>481112</v>
       </c>
       <c r="R25" t="n">
-        <v>6784502</v>
+        <v>6784721</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3309,10 +3309,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119741440</v>
+        <v>119741905</v>
       </c>
       <c r="B26" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,25 +3321,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,7 +3355,7 @@
         <v>6784535</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119741905</v>
+        <v>119741440</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3433,25 +3433,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
         <v>6784535</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,7 +3533,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119788935</v>
+        <v>119789105</v>
       </c>
       <c r="B28" t="n">
         <v>91856</v>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480987</v>
+        <v>481038</v>
       </c>
       <c r="R28" t="n">
-        <v>6784663</v>
+        <v>6784721</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3635,7 +3635,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119787115</v>
+        <v>119788082</v>
       </c>
       <c r="B29" t="n">
         <v>91856</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481178</v>
+        <v>481144</v>
       </c>
       <c r="R29" t="n">
-        <v>6784510</v>
+        <v>6784602</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119787002</v>
+        <v>119787665</v>
       </c>
       <c r="B30" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481114</v>
+        <v>481287</v>
       </c>
       <c r="R30" t="n">
-        <v>6784523</v>
+        <v>6784633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3839,7 +3839,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119788908</v>
+        <v>119787833</v>
       </c>
       <c r="B31" t="n">
         <v>78526</v>
@@ -3875,14 +3875,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481028</v>
+        <v>481250</v>
       </c>
       <c r="R31" t="n">
-        <v>6784697</v>
+        <v>6784659</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,9 +3912,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,22 +3939,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788662</v>
+        <v>119787807</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3953,38 +3963,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481133</v>
+        <v>481250</v>
       </c>
       <c r="R32" t="n">
-        <v>6784731</v>
+        <v>6784659</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,9 +4024,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4031,19 +4051,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119787774</v>
+        <v>119789064</v>
       </c>
       <c r="B33" t="n">
         <v>91884</v>
@@ -4083,10 +4103,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481250</v>
+        <v>481010</v>
       </c>
       <c r="R33" t="n">
-        <v>6784627</v>
+        <v>6784679</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4145,10 +4165,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119788550</v>
+        <v>119787790</v>
       </c>
       <c r="B34" t="n">
-        <v>90067</v>
+        <v>91834</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4157,47 +4177,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481050</v>
+        <v>481260</v>
       </c>
       <c r="R34" t="n">
-        <v>6784604</v>
+        <v>6784612</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4227,19 +4238,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4254,22 +4255,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119787167</v>
+        <v>119787470</v>
       </c>
       <c r="B35" t="n">
-        <v>91856</v>
+        <v>91821</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4278,25 +4279,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>6055</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481197</v>
+        <v>481284</v>
       </c>
       <c r="R35" t="n">
-        <v>6784509</v>
+        <v>6784549</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4368,7 +4369,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119787807</v>
+        <v>119786882</v>
       </c>
       <c r="B36" t="n">
         <v>91856</v>
@@ -4404,14 +4405,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481250</v>
+        <v>481048</v>
       </c>
       <c r="R36" t="n">
-        <v>6784659</v>
+        <v>6784513</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4441,19 +4442,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4468,22 +4459,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119787759</v>
+        <v>119789077</v>
       </c>
       <c r="B37" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4496,21 +4487,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4520,10 +4511,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481248</v>
+        <v>481052</v>
       </c>
       <c r="R37" t="n">
-        <v>6784628</v>
+        <v>6784759</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4570,22 +4561,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119787135</v>
+        <v>119788104</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>8432</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4594,38 +4585,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481048</v>
+        <v>481122</v>
       </c>
       <c r="R38" t="n">
-        <v>6784513</v>
+        <v>6784602</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4672,22 +4668,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119788928</v>
+        <v>119787115</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4700,21 +4696,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4724,10 +4720,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481138</v>
+        <v>481178</v>
       </c>
       <c r="R39" t="n">
-        <v>6784747</v>
+        <v>6784510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4774,22 +4770,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119788782</v>
+        <v>119787759</v>
       </c>
       <c r="B40" t="n">
-        <v>91863</v>
+        <v>79144</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4802,43 +4798,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481195</v>
+        <v>481248</v>
       </c>
       <c r="R40" t="n">
-        <v>6784739</v>
+        <v>6784628</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4868,19 +4855,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4895,19 +4872,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119787644</v>
+        <v>119788786</v>
       </c>
       <c r="B41" t="n">
         <v>78526</v>
@@ -4947,10 +4924,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481277</v>
+        <v>481176</v>
       </c>
       <c r="R41" t="n">
-        <v>6784621</v>
+        <v>6784737</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5009,10 +4986,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119788514</v>
+        <v>119788908</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5021,25 +4998,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5049,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481088</v>
+        <v>481028</v>
       </c>
       <c r="R42" t="n">
-        <v>6784614</v>
+        <v>6784697</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5099,19 +5076,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119788519</v>
+        <v>119789016</v>
       </c>
       <c r="B43" t="n">
         <v>91840</v>
@@ -5151,10 +5128,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481087</v>
+        <v>480995</v>
       </c>
       <c r="R43" t="n">
-        <v>6784724</v>
+        <v>6784692</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5213,10 +5190,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119786882</v>
+        <v>119787764</v>
       </c>
       <c r="B44" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5229,21 +5206,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5253,10 +5230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481048</v>
+        <v>481252</v>
       </c>
       <c r="R44" t="n">
-        <v>6784513</v>
+        <v>6784627</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5303,22 +5280,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119789064</v>
+        <v>119788782</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>91863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5331,34 +5308,43 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481010</v>
+        <v>481195</v>
       </c>
       <c r="R45" t="n">
-        <v>6784679</v>
+        <v>6784739</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5388,9 +5374,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5405,22 +5401,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119786836</v>
+        <v>119788776</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5433,21 +5429,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5457,10 +5453,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481049</v>
+        <v>481179</v>
       </c>
       <c r="R46" t="n">
-        <v>6784514</v>
+        <v>6784744</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5519,10 +5515,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119787740</v>
+        <v>119787028</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5531,25 +5527,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5559,10 +5555,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481276</v>
+        <v>481150</v>
       </c>
       <c r="R47" t="n">
-        <v>6784646</v>
+        <v>6784524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5609,22 +5605,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119788786</v>
+        <v>119788565</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5633,25 +5629,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5661,10 +5657,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481176</v>
+        <v>481108</v>
       </c>
       <c r="R48" t="n">
-        <v>6784737</v>
+        <v>6784708</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5711,22 +5707,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119787744</v>
+        <v>119788094</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5735,41 +5731,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481267</v>
+        <v>481132</v>
       </c>
       <c r="R49" t="n">
-        <v>6784656</v>
+        <v>6784594</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5796,19 +5792,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5823,22 +5809,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119788483</v>
+        <v>119787544</v>
       </c>
       <c r="B50" t="n">
-        <v>89275</v>
+        <v>8432</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5847,38 +5833,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6286</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481050</v>
+        <v>481291</v>
       </c>
       <c r="R50" t="n">
-        <v>6784604</v>
+        <v>6784590</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5910,7 +5905,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5920,7 +5915,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5929,6 +5924,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5947,10 +5943,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119789066</v>
+        <v>119787139</v>
       </c>
       <c r="B51" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5963,21 +5959,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5987,10 +5983,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480996</v>
+        <v>481215</v>
       </c>
       <c r="R51" t="n">
-        <v>6784667</v>
+        <v>6784513</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6022,7 +6018,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6032,7 +6028,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6059,10 +6055,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119787715</v>
+        <v>119788312</v>
       </c>
       <c r="B52" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6075,21 +6071,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6099,10 +6095,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481274</v>
+        <v>481062</v>
       </c>
       <c r="R52" t="n">
-        <v>6784652</v>
+        <v>6784614</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6149,22 +6145,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119787771</v>
+        <v>119788483</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>89275</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6173,38 +6169,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481276</v>
+        <v>481050</v>
       </c>
       <c r="R53" t="n">
-        <v>6784646</v>
+        <v>6784604</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6234,9 +6230,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6251,22 +6257,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119787764</v>
+        <v>119789074</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6275,25 +6281,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6303,10 +6309,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481252</v>
+        <v>481031</v>
       </c>
       <c r="R54" t="n">
-        <v>6784627</v>
+        <v>6784712</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6365,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119788571</v>
+        <v>119789434</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6381,34 +6387,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481088</v>
+        <v>481002</v>
       </c>
       <c r="R55" t="n">
-        <v>6784614</v>
+        <v>6784693</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6438,9 +6449,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6455,22 +6476,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119788094</v>
+        <v>119786836</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6479,25 +6500,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6507,10 +6528,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481132</v>
+        <v>481049</v>
       </c>
       <c r="R56" t="n">
-        <v>6784594</v>
+        <v>6784514</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6557,22 +6578,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119788715</v>
+        <v>119787021</v>
       </c>
       <c r="B57" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6585,34 +6606,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481104</v>
+        <v>481048</v>
       </c>
       <c r="R57" t="n">
-        <v>6784681</v>
+        <v>6784513</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6642,19 +6663,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6669,22 +6680,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119789077</v>
+        <v>119788774</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>88153</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6697,34 +6708,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4962</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481052</v>
+        <v>481195</v>
       </c>
       <c r="R58" t="n">
-        <v>6784759</v>
+        <v>6784739</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6754,9 +6765,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6771,22 +6792,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119789105</v>
+        <v>119792265</v>
       </c>
       <c r="B59" t="n">
-        <v>91856</v>
+        <v>89239</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6795,41 +6816,48 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>6268</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481038</v>
+        <v>481044</v>
       </c>
       <c r="R59" t="n">
-        <v>6784721</v>
+        <v>6784736</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6867,28 +6895,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119788305</v>
+        <v>119787740</v>
       </c>
       <c r="B60" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6897,41 +6926,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481083</v>
+        <v>481276</v>
       </c>
       <c r="R60" t="n">
-        <v>6784643</v>
+        <v>6784646</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6958,19 +6987,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6985,22 +7004,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119788846</v>
+        <v>119788715</v>
       </c>
       <c r="B61" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7013,34 +7032,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481139</v>
+        <v>481104</v>
       </c>
       <c r="R61" t="n">
-        <v>6784744</v>
+        <v>6784681</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7070,9 +7089,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7087,22 +7116,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119789434</v>
+        <v>119788560</v>
       </c>
       <c r="B62" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7115,39 +7144,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481002</v>
+        <v>481088</v>
       </c>
       <c r="R62" t="n">
-        <v>6784693</v>
+        <v>6784614</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7177,19 +7201,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7204,22 +7218,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119789001</v>
+        <v>119786992</v>
       </c>
       <c r="B63" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7228,25 +7242,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7256,10 +7270,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481138</v>
+        <v>481048</v>
       </c>
       <c r="R63" t="n">
-        <v>6784747</v>
+        <v>6784513</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7318,10 +7332,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119787833</v>
+        <v>119787002</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7334,34 +7348,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481250</v>
+        <v>481114</v>
       </c>
       <c r="R64" t="n">
-        <v>6784659</v>
+        <v>6784523</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7391,19 +7405,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7418,22 +7422,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119792265</v>
+        <v>119787770</v>
       </c>
       <c r="B65" t="n">
-        <v>89239</v>
+        <v>91856</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7442,48 +7446,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6268</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481044</v>
+        <v>481267</v>
       </c>
       <c r="R65" t="n">
-        <v>6784736</v>
+        <v>6784656</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7510,18 +7507,27 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7540,10 +7546,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119788565</v>
+        <v>119787681</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7552,25 +7558,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7580,10 +7586,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481108</v>
+        <v>481294</v>
       </c>
       <c r="R66" t="n">
-        <v>6784708</v>
+        <v>6784626</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7642,10 +7648,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119788033</v>
+        <v>119787774</v>
       </c>
       <c r="B67" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7658,21 +7664,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7682,10 +7688,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481181</v>
+        <v>481250</v>
       </c>
       <c r="R67" t="n">
-        <v>6784644</v>
+        <v>6784627</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119789016</v>
+        <v>119787167</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7756,25 +7762,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7784,10 +7790,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480995</v>
+        <v>481197</v>
       </c>
       <c r="R68" t="n">
-        <v>6784692</v>
+        <v>6784509</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7846,10 +7852,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119789074</v>
+        <v>119788574</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7862,34 +7868,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481031</v>
+        <v>481104</v>
       </c>
       <c r="R69" t="n">
-        <v>6784712</v>
+        <v>6784681</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7919,9 +7930,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7936,19 +7957,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119788851</v>
+        <v>119787827</v>
       </c>
       <c r="B70" t="n">
         <v>91840</v>
@@ -7984,14 +8005,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481136</v>
+        <v>481229</v>
       </c>
       <c r="R70" t="n">
-        <v>6784750</v>
+        <v>6784643</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8021,19 +8042,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8048,22 +8059,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119788774</v>
+        <v>119789001</v>
       </c>
       <c r="B71" t="n">
-        <v>88153</v>
+        <v>91856</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8076,34 +8087,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4962</v>
+        <v>2059</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481195</v>
+        <v>481138</v>
       </c>
       <c r="R71" t="n">
-        <v>6784739</v>
+        <v>6784747</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8133,19 +8144,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8160,22 +8161,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119788574</v>
+        <v>119787935</v>
       </c>
       <c r="B72" t="n">
-        <v>8432</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8184,43 +8185,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481104</v>
+        <v>481160</v>
       </c>
       <c r="R72" t="n">
-        <v>6784681</v>
+        <v>6784611</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8250,19 +8246,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8277,22 +8263,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119787827</v>
+        <v>119788482</v>
       </c>
       <c r="B73" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8301,25 +8287,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8329,10 +8315,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481229</v>
+        <v>481092</v>
       </c>
       <c r="R73" t="n">
-        <v>6784643</v>
+        <v>6784610</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8391,10 +8377,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119787935</v>
+        <v>119788550</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>90067</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8403,38 +8389,47 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481160</v>
+        <v>481050</v>
       </c>
       <c r="R74" t="n">
-        <v>6784611</v>
+        <v>6784604</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8464,9 +8459,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8481,22 +8486,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119787139</v>
+        <v>119787848</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8505,38 +8510,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481215</v>
+        <v>481187</v>
       </c>
       <c r="R75" t="n">
-        <v>6784513</v>
+        <v>6784640</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8566,19 +8571,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8593,22 +8588,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119788482</v>
+        <v>119788514</v>
       </c>
       <c r="B76" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8617,25 +8612,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8645,10 +8640,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481092</v>
+        <v>481088</v>
       </c>
       <c r="R76" t="n">
-        <v>6784610</v>
+        <v>6784614</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8695,22 +8690,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119788104</v>
+        <v>119788519</v>
       </c>
       <c r="B77" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8723,39 +8718,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481122</v>
+        <v>481087</v>
       </c>
       <c r="R77" t="n">
-        <v>6784602</v>
+        <v>6784724</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8814,7 +8804,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119787770</v>
+        <v>119789066</v>
       </c>
       <c r="B78" t="n">
         <v>91856</v>
@@ -8854,10 +8844,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481267</v>
+        <v>480996</v>
       </c>
       <c r="R78" t="n">
-        <v>6784656</v>
+        <v>6784667</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8889,7 +8879,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8899,7 +8889,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8926,10 +8916,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119787028</v>
+        <v>119788305</v>
       </c>
       <c r="B79" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8942,37 +8932,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481150</v>
+        <v>481083</v>
       </c>
       <c r="R79" t="n">
-        <v>6784524</v>
+        <v>6784643</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8999,9 +8989,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9016,22 +9016,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119788312</v>
+        <v>119788935</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9044,21 +9044,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9068,10 +9068,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481062</v>
+        <v>480987</v>
       </c>
       <c r="R80" t="n">
-        <v>6784614</v>
+        <v>6784663</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9118,22 +9118,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119787681</v>
+        <v>119788662</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9142,25 +9142,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9170,10 +9170,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481294</v>
+        <v>481133</v>
       </c>
       <c r="R81" t="n">
-        <v>6784626</v>
+        <v>6784731</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9232,10 +9232,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119787848</v>
+        <v>119787644</v>
       </c>
       <c r="B82" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9244,25 +9244,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481187</v>
+        <v>481277</v>
       </c>
       <c r="R82" t="n">
-        <v>6784640</v>
+        <v>6784621</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9322,22 +9322,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119786992</v>
+        <v>119788033</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9346,25 +9346,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9374,10 +9374,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481048</v>
+        <v>481181</v>
       </c>
       <c r="R83" t="n">
-        <v>6784513</v>
+        <v>6784644</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9424,22 +9424,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119787470</v>
+        <v>119788846</v>
       </c>
       <c r="B84" t="n">
-        <v>91821</v>
+        <v>91832</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9448,25 +9448,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6055</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481284</v>
+        <v>481139</v>
       </c>
       <c r="R84" t="n">
-        <v>6784549</v>
+        <v>6784744</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9538,7 +9538,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788950</v>
+        <v>119788851</v>
       </c>
       <c r="B85" t="n">
         <v>91840</v>
@@ -9578,10 +9578,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>480996</v>
+        <v>481136</v>
       </c>
       <c r="R85" t="n">
-        <v>6784667</v>
+        <v>6784750</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9650,10 +9650,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119787544</v>
+        <v>119787715</v>
       </c>
       <c r="B86" t="n">
-        <v>8432</v>
+        <v>91884</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9662,47 +9662,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481291</v>
+        <v>481274</v>
       </c>
       <c r="R86" t="n">
-        <v>6784590</v>
+        <v>6784652</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9732,50 +9723,39 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788776</v>
+        <v>119787771</v>
       </c>
       <c r="B87" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9788,21 +9768,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9812,10 +9792,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481179</v>
+        <v>481276</v>
       </c>
       <c r="R87" t="n">
-        <v>6784744</v>
+        <v>6784646</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9862,22 +9842,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119787665</v>
+        <v>119788928</v>
       </c>
       <c r="B88" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9890,21 +9870,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9914,10 +9894,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481287</v>
+        <v>481138</v>
       </c>
       <c r="R88" t="n">
-        <v>6784633</v>
+        <v>6784747</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9964,22 +9944,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119787790</v>
+        <v>119787744</v>
       </c>
       <c r="B89" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9992,37 +9972,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481260</v>
+        <v>481267</v>
       </c>
       <c r="R89" t="n">
-        <v>6784612</v>
+        <v>6784656</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10049,9 +10029,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10066,22 +10056,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119788082</v>
+        <v>119787094</v>
       </c>
       <c r="B90" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10090,25 +10080,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10118,10 +10108,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481144</v>
+        <v>481175</v>
       </c>
       <c r="R90" t="n">
-        <v>6784602</v>
+        <v>6784516</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10180,7 +10170,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119787094</v>
+        <v>119788950</v>
       </c>
       <c r="B91" t="n">
         <v>91840</v>
@@ -10216,14 +10206,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481175</v>
+        <v>480996</v>
       </c>
       <c r="R91" t="n">
-        <v>6784516</v>
+        <v>6784667</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10253,9 +10243,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10270,12 +10270,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -2987,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706741</v>
+        <v>119706870</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2999,28 +2999,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3030,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481017</v>
+        <v>481067</v>
       </c>
       <c r="R23" t="n">
-        <v>6784518</v>
+        <v>6784504</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3093,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706870</v>
+        <v>119706741</v>
       </c>
       <c r="B24" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3105,32 +3109,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481067</v>
+        <v>481017</v>
       </c>
       <c r="R24" t="n">
-        <v>6784504</v>
+        <v>6784518</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119788104</v>
+        <v>119787115</v>
       </c>
       <c r="B38" t="n">
-        <v>8432</v>
+        <v>91856</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4585,43 +4585,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481122</v>
+        <v>481178</v>
       </c>
       <c r="R38" t="n">
-        <v>6784602</v>
+        <v>6784510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,10 +4675,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119787115</v>
+        <v>119789016</v>
       </c>
       <c r="B39" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4692,25 +4687,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4720,10 +4715,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481178</v>
+        <v>480995</v>
       </c>
       <c r="R39" t="n">
-        <v>6784510</v>
+        <v>6784692</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,10 +5083,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119789016</v>
+        <v>119788104</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5104,34 +5099,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480995</v>
+        <v>481122</v>
       </c>
       <c r="R43" t="n">
-        <v>6784692</v>
+        <v>6784602</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119788782</v>
+        <v>119787544</v>
       </c>
       <c r="B45" t="n">
-        <v>91863</v>
+        <v>8432</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,47 +5304,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481195</v>
+        <v>481291</v>
       </c>
       <c r="R45" t="n">
-        <v>6784739</v>
+        <v>6784590</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5395,6 +5395,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5413,10 +5414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788776</v>
+        <v>119788782</v>
       </c>
       <c r="B46" t="n">
-        <v>91856</v>
+        <v>91863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5429,34 +5430,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481179</v>
+        <v>481195</v>
       </c>
       <c r="R46" t="n">
-        <v>6784744</v>
+        <v>6784739</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5486,9 +5496,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5503,19 +5523,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119787028</v>
+        <v>119788776</v>
       </c>
       <c r="B47" t="n">
         <v>91856</v>
@@ -5555,10 +5575,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481150</v>
+        <v>481179</v>
       </c>
       <c r="R47" t="n">
-        <v>6784524</v>
+        <v>6784744</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5617,10 +5637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119788565</v>
+        <v>119787028</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5629,25 +5649,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,10 +5677,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481108</v>
+        <v>481150</v>
       </c>
       <c r="R48" t="n">
-        <v>6784708</v>
+        <v>6784524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5719,7 +5739,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788094</v>
+        <v>119788565</v>
       </c>
       <c r="B49" t="n">
         <v>91840</v>
@@ -5759,10 +5779,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481132</v>
+        <v>481108</v>
       </c>
       <c r="R49" t="n">
-        <v>6784594</v>
+        <v>6784708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,22 +5829,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119787544</v>
+        <v>119788094</v>
       </c>
       <c r="B50" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5837,43 +5857,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481291</v>
+        <v>481132</v>
       </c>
       <c r="R50" t="n">
-        <v>6784590</v>
+        <v>6784594</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5903,40 +5914,29 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -8071,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119789001</v>
+        <v>119788482</v>
       </c>
       <c r="B71" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8083,25 +8083,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481138</v>
+        <v>481092</v>
       </c>
       <c r="R71" t="n">
-        <v>6784747</v>
+        <v>6784610</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,22 +8161,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119787935</v>
+        <v>119789001</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8189,21 +8189,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481160</v>
+        <v>481138</v>
       </c>
       <c r="R72" t="n">
-        <v>6784611</v>
+        <v>6784747</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8275,10 +8275,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119788482</v>
+        <v>119787935</v>
       </c>
       <c r="B73" t="n">
-        <v>89275</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8287,25 +8287,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6286</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8315,10 +8315,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481092</v>
+        <v>481160</v>
       </c>
       <c r="R73" t="n">
-        <v>6784610</v>
+        <v>6784611</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8365,12 +8365,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788846</v>
+        <v>119787771</v>
       </c>
       <c r="B84" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9452,21 +9452,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481139</v>
+        <v>481276</v>
       </c>
       <c r="R84" t="n">
-        <v>6784744</v>
+        <v>6784646</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9526,22 +9526,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788851</v>
+        <v>119788928</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9550,38 +9550,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481136</v>
+        <v>481138</v>
       </c>
       <c r="R85" t="n">
-        <v>6784750</v>
+        <v>6784747</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,19 +9611,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9638,22 +9628,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119787715</v>
+        <v>119788846</v>
       </c>
       <c r="B86" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9666,21 +9656,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9690,10 +9680,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481274</v>
+        <v>481139</v>
       </c>
       <c r="R86" t="n">
-        <v>6784652</v>
+        <v>6784744</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9752,10 +9742,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119787771</v>
+        <v>119788851</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9764,38 +9754,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481276</v>
+        <v>481136</v>
       </c>
       <c r="R87" t="n">
-        <v>6784646</v>
+        <v>6784750</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9825,9 +9815,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9842,22 +9842,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119788928</v>
+        <v>119787715</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9870,21 +9870,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481138</v>
+        <v>481274</v>
       </c>
       <c r="R88" t="n">
-        <v>6784747</v>
+        <v>6784652</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9944,12 +9944,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -4573,10 +4573,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119787115</v>
+        <v>119788104</v>
       </c>
       <c r="B38" t="n">
-        <v>91856</v>
+        <v>8432</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4585,38 +4585,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481178</v>
+        <v>481122</v>
       </c>
       <c r="R38" t="n">
-        <v>6784510</v>
+        <v>6784602</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4675,10 +4680,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119789016</v>
+        <v>119787115</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4687,25 +4692,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4715,10 +4720,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480995</v>
+        <v>481178</v>
       </c>
       <c r="R39" t="n">
-        <v>6784692</v>
+        <v>6784510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5083,10 +5088,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119788104</v>
+        <v>119789016</v>
       </c>
       <c r="B43" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5099,39 +5104,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481122</v>
+        <v>480995</v>
       </c>
       <c r="R43" t="n">
-        <v>6784602</v>
+        <v>6784692</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119787544</v>
+        <v>119788782</v>
       </c>
       <c r="B45" t="n">
-        <v>8432</v>
+        <v>91863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,47 +5304,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481291</v>
+        <v>481195</v>
       </c>
       <c r="R45" t="n">
-        <v>6784590</v>
+        <v>6784739</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5395,7 +5395,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788782</v>
+        <v>119788776</v>
       </c>
       <c r="B46" t="n">
-        <v>91863</v>
+        <v>91856</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5430,43 +5429,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481195</v>
+        <v>481179</v>
       </c>
       <c r="R46" t="n">
-        <v>6784739</v>
+        <v>6784744</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5496,19 +5486,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5523,19 +5503,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119788776</v>
+        <v>119787028</v>
       </c>
       <c r="B47" t="n">
         <v>91856</v>
@@ -5575,10 +5555,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481179</v>
+        <v>481150</v>
       </c>
       <c r="R47" t="n">
-        <v>6784744</v>
+        <v>6784524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5637,10 +5617,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119787028</v>
+        <v>119788565</v>
       </c>
       <c r="B48" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5649,25 +5629,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,10 +5657,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481150</v>
+        <v>481108</v>
       </c>
       <c r="R48" t="n">
-        <v>6784524</v>
+        <v>6784708</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5739,7 +5719,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788565</v>
+        <v>119788094</v>
       </c>
       <c r="B49" t="n">
         <v>91840</v>
@@ -5779,10 +5759,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481108</v>
+        <v>481132</v>
       </c>
       <c r="R49" t="n">
-        <v>6784708</v>
+        <v>6784594</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,22 +5809,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119788094</v>
+        <v>119787544</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5857,34 +5837,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481132</v>
+        <v>481291</v>
       </c>
       <c r="R50" t="n">
-        <v>6784594</v>
+        <v>6784590</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5914,29 +5903,40 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119789434</v>
+        <v>119786836</v>
       </c>
       <c r="B55" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,39 +6387,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481002</v>
+        <v>481049</v>
       </c>
       <c r="R55" t="n">
-        <v>6784693</v>
+        <v>6784514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6449,19 +6444,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6476,19 +6461,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119786836</v>
+        <v>119787021</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6528,10 +6513,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481049</v>
+        <v>481048</v>
       </c>
       <c r="R56" t="n">
-        <v>6784514</v>
+        <v>6784513</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6578,22 +6563,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119787021</v>
+        <v>119789434</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6606,34 +6591,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481048</v>
+        <v>481002</v>
       </c>
       <c r="R57" t="n">
-        <v>6784513</v>
+        <v>6784693</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6663,9 +6653,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,12 +6680,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -8071,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119788482</v>
+        <v>119789001</v>
       </c>
       <c r="B71" t="n">
-        <v>89275</v>
+        <v>91856</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8083,25 +8083,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481092</v>
+        <v>481138</v>
       </c>
       <c r="R71" t="n">
-        <v>6784610</v>
+        <v>6784747</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,22 +8161,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119789001</v>
+        <v>119787935</v>
       </c>
       <c r="B72" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8189,21 +8189,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481138</v>
+        <v>481160</v>
       </c>
       <c r="R72" t="n">
-        <v>6784747</v>
+        <v>6784611</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8275,10 +8275,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119787935</v>
+        <v>119788482</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>89275</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8287,25 +8287,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8315,10 +8315,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481160</v>
+        <v>481092</v>
       </c>
       <c r="R73" t="n">
-        <v>6784611</v>
+        <v>6784610</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8365,12 +8365,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8916,10 +8916,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788305</v>
+        <v>119788935</v>
       </c>
       <c r="B79" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8932,37 +8932,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481083</v>
+        <v>480987</v>
       </c>
       <c r="R79" t="n">
-        <v>6784643</v>
+        <v>6784663</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8989,19 +8989,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9016,22 +9006,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119788935</v>
+        <v>119787644</v>
       </c>
       <c r="B80" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9044,21 +9034,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9068,10 +9058,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480987</v>
+        <v>481277</v>
       </c>
       <c r="R80" t="n">
-        <v>6784663</v>
+        <v>6784621</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9118,12 +9108,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9232,10 +9222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119787644</v>
+        <v>119788305</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9248,37 +9238,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481277</v>
+        <v>481083</v>
       </c>
       <c r="R82" t="n">
-        <v>6784621</v>
+        <v>6784643</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9305,9 +9295,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9322,12 +9322,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119787771</v>
+        <v>119788846</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9452,21 +9452,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481276</v>
+        <v>481139</v>
       </c>
       <c r="R84" t="n">
-        <v>6784646</v>
+        <v>6784744</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9526,22 +9526,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788928</v>
+        <v>119788851</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9550,38 +9550,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481138</v>
+        <v>481136</v>
       </c>
       <c r="R85" t="n">
-        <v>6784747</v>
+        <v>6784750</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,9 +9611,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9628,22 +9638,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788846</v>
+        <v>119787715</v>
       </c>
       <c r="B86" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9656,21 +9666,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9680,10 +9690,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481139</v>
+        <v>481274</v>
       </c>
       <c r="R86" t="n">
-        <v>6784744</v>
+        <v>6784652</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,10 +9752,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788851</v>
+        <v>119787771</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9754,38 +9764,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481136</v>
+        <v>481276</v>
       </c>
       <c r="R87" t="n">
-        <v>6784750</v>
+        <v>6784646</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9815,19 +9825,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9842,22 +9842,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119787715</v>
+        <v>119788928</v>
       </c>
       <c r="B88" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9870,21 +9870,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481274</v>
+        <v>481138</v>
       </c>
       <c r="R88" t="n">
-        <v>6784652</v>
+        <v>6784747</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9944,12 +9944,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119683489</v>
+        <v>119683503</v>
       </c>
       <c r="B5" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,28 +1047,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1077,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481045</v>
+        <v>481058</v>
       </c>
       <c r="R5" t="n">
-        <v>6784589</v>
+        <v>6784561</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119683503</v>
+        <v>119683489</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,37 +1171,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481058</v>
+        <v>481045</v>
       </c>
       <c r="R6" t="n">
-        <v>6784561</v>
+        <v>6784589</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2987,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706870</v>
+        <v>119706741</v>
       </c>
       <c r="B23" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2999,32 +2999,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3034,10 +3030,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481067</v>
+        <v>481017</v>
       </c>
       <c r="R23" t="n">
-        <v>6784504</v>
+        <v>6784518</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3097,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706741</v>
+        <v>119706870</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3109,28 +3105,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481017</v>
+        <v>481067</v>
       </c>
       <c r="R24" t="n">
-        <v>6784518</v>
+        <v>6784504</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119788104</v>
+        <v>119787115</v>
       </c>
       <c r="B38" t="n">
-        <v>8432</v>
+        <v>91856</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4585,43 +4585,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481122</v>
+        <v>481178</v>
       </c>
       <c r="R38" t="n">
-        <v>6784602</v>
+        <v>6784510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4680,10 +4675,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119787115</v>
+        <v>119789016</v>
       </c>
       <c r="B39" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4692,25 +4687,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4720,10 +4715,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481178</v>
+        <v>480995</v>
       </c>
       <c r="R39" t="n">
-        <v>6784510</v>
+        <v>6784692</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5088,10 +5083,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119789016</v>
+        <v>119788104</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5104,34 +5099,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480995</v>
+        <v>481122</v>
       </c>
       <c r="R43" t="n">
-        <v>6784692</v>
+        <v>6784602</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119788782</v>
+        <v>119787544</v>
       </c>
       <c r="B45" t="n">
-        <v>91863</v>
+        <v>8432</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,47 +5304,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481195</v>
+        <v>481291</v>
       </c>
       <c r="R45" t="n">
-        <v>6784739</v>
+        <v>6784590</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5395,6 +5395,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5413,10 +5414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788776</v>
+        <v>119788782</v>
       </c>
       <c r="B46" t="n">
-        <v>91856</v>
+        <v>91863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5429,34 +5430,43 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481179</v>
+        <v>481195</v>
       </c>
       <c r="R46" t="n">
-        <v>6784744</v>
+        <v>6784739</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5486,9 +5496,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5503,19 +5523,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119787028</v>
+        <v>119788776</v>
       </c>
       <c r="B47" t="n">
         <v>91856</v>
@@ -5555,10 +5575,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481150</v>
+        <v>481179</v>
       </c>
       <c r="R47" t="n">
-        <v>6784524</v>
+        <v>6784744</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5617,10 +5637,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119788565</v>
+        <v>119787028</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5629,25 +5649,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,10 +5677,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481108</v>
+        <v>481150</v>
       </c>
       <c r="R48" t="n">
-        <v>6784708</v>
+        <v>6784524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5719,7 +5739,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788094</v>
+        <v>119788565</v>
       </c>
       <c r="B49" t="n">
         <v>91840</v>
@@ -5759,10 +5779,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481132</v>
+        <v>481108</v>
       </c>
       <c r="R49" t="n">
-        <v>6784594</v>
+        <v>6784708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,22 +5829,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119787544</v>
+        <v>119788094</v>
       </c>
       <c r="B50" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5837,43 +5857,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481291</v>
+        <v>481132</v>
       </c>
       <c r="R50" t="n">
-        <v>6784590</v>
+        <v>6784594</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5903,40 +5914,29 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119786836</v>
+        <v>119789434</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,34 +6387,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481049</v>
+        <v>481002</v>
       </c>
       <c r="R55" t="n">
-        <v>6784514</v>
+        <v>6784693</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,9 +6449,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,19 +6476,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119787021</v>
+        <v>119786836</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6513,10 +6528,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481048</v>
+        <v>481049</v>
       </c>
       <c r="R56" t="n">
-        <v>6784513</v>
+        <v>6784514</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6563,22 +6578,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119789434</v>
+        <v>119787021</v>
       </c>
       <c r="B57" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6591,39 +6606,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481002</v>
+        <v>481048</v>
       </c>
       <c r="R57" t="n">
-        <v>6784693</v>
+        <v>6784513</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6653,19 +6663,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,12 +6680,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119787770</v>
+        <v>119787681</v>
       </c>
       <c r="B65" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7450,34 +7450,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481267</v>
+        <v>481294</v>
       </c>
       <c r="R65" t="n">
-        <v>6784656</v>
+        <v>6784626</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7507,19 +7507,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7534,22 +7524,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119787681</v>
+        <v>119787770</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7562,34 +7552,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481294</v>
+        <v>481267</v>
       </c>
       <c r="R66" t="n">
-        <v>6784626</v>
+        <v>6784656</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7619,9 +7609,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7636,12 +7636,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -4165,10 +4165,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119787790</v>
+        <v>119786882</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481260</v>
+        <v>481048</v>
       </c>
       <c r="R34" t="n">
-        <v>6784612</v>
+        <v>6784513</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4255,22 +4255,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119787470</v>
+        <v>119789077</v>
       </c>
       <c r="B35" t="n">
-        <v>91821</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4279,25 +4279,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6055</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481284</v>
+        <v>481052</v>
       </c>
       <c r="R35" t="n">
-        <v>6784549</v>
+        <v>6784759</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4357,22 +4357,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119786882</v>
+        <v>119787790</v>
       </c>
       <c r="B36" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4385,21 +4385,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481048</v>
+        <v>481260</v>
       </c>
       <c r="R36" t="n">
-        <v>6784513</v>
+        <v>6784612</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4459,22 +4459,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119789077</v>
+        <v>119787470</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>91821</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4483,25 +4483,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6055</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481052</v>
+        <v>481284</v>
       </c>
       <c r="R37" t="n">
-        <v>6784759</v>
+        <v>6784549</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4561,12 +4561,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119787544</v>
+        <v>119788782</v>
       </c>
       <c r="B45" t="n">
-        <v>8432</v>
+        <v>91863</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5304,47 +5304,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481291</v>
+        <v>481195</v>
       </c>
       <c r="R45" t="n">
-        <v>6784590</v>
+        <v>6784739</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5395,7 +5395,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5413,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788782</v>
+        <v>119788776</v>
       </c>
       <c r="B46" t="n">
-        <v>91863</v>
+        <v>91856</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5430,43 +5429,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481195</v>
+        <v>481179</v>
       </c>
       <c r="R46" t="n">
-        <v>6784739</v>
+        <v>6784744</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5496,19 +5486,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5523,19 +5503,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119788776</v>
+        <v>119787028</v>
       </c>
       <c r="B47" t="n">
         <v>91856</v>
@@ -5575,10 +5555,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481179</v>
+        <v>481150</v>
       </c>
       <c r="R47" t="n">
-        <v>6784744</v>
+        <v>6784524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5637,10 +5617,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119787028</v>
+        <v>119788565</v>
       </c>
       <c r="B48" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5649,25 +5629,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5677,10 +5657,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481150</v>
+        <v>481108</v>
       </c>
       <c r="R48" t="n">
-        <v>6784524</v>
+        <v>6784708</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5739,7 +5719,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788565</v>
+        <v>119788094</v>
       </c>
       <c r="B49" t="n">
         <v>91840</v>
@@ -5779,10 +5759,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481108</v>
+        <v>481132</v>
       </c>
       <c r="R49" t="n">
-        <v>6784708</v>
+        <v>6784594</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5829,22 +5809,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119788094</v>
+        <v>119787544</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5857,34 +5837,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481132</v>
+        <v>481291</v>
       </c>
       <c r="R50" t="n">
-        <v>6784594</v>
+        <v>6784590</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5914,29 +5903,40 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119789434</v>
+        <v>119786836</v>
       </c>
       <c r="B55" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,39 +6387,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481002</v>
+        <v>481049</v>
       </c>
       <c r="R55" t="n">
-        <v>6784693</v>
+        <v>6784514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6449,19 +6444,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6476,19 +6461,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119786836</v>
+        <v>119787021</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6528,10 +6513,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481049</v>
+        <v>481048</v>
       </c>
       <c r="R56" t="n">
-        <v>6784514</v>
+        <v>6784513</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6578,22 +6563,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119787021</v>
+        <v>119789434</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6606,34 +6591,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481048</v>
+        <v>481002</v>
       </c>
       <c r="R57" t="n">
-        <v>6784513</v>
+        <v>6784693</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6663,9 +6653,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,12 +6680,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119787681</v>
+        <v>119787770</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7450,34 +7450,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481294</v>
+        <v>481267</v>
       </c>
       <c r="R65" t="n">
-        <v>6784626</v>
+        <v>6784656</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7507,9 +7507,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7524,22 +7534,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119787770</v>
+        <v>119787681</v>
       </c>
       <c r="B66" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7552,34 +7562,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481267</v>
+        <v>481294</v>
       </c>
       <c r="R66" t="n">
-        <v>6784656</v>
+        <v>6784626</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7609,19 +7619,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7636,12 +7636,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8071,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119789001</v>
+        <v>119788482</v>
       </c>
       <c r="B71" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8083,25 +8083,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481138</v>
+        <v>481092</v>
       </c>
       <c r="R71" t="n">
-        <v>6784747</v>
+        <v>6784610</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,22 +8161,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119787935</v>
+        <v>119789001</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8189,21 +8189,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481160</v>
+        <v>481138</v>
       </c>
       <c r="R72" t="n">
-        <v>6784611</v>
+        <v>6784747</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8275,10 +8275,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119788482</v>
+        <v>119787935</v>
       </c>
       <c r="B73" t="n">
-        <v>89275</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8287,25 +8287,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6286</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8315,10 +8315,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481092</v>
+        <v>481160</v>
       </c>
       <c r="R73" t="n">
-        <v>6784610</v>
+        <v>6784611</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8365,22 +8365,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119788550</v>
+        <v>119789066</v>
       </c>
       <c r="B74" t="n">
-        <v>90067</v>
+        <v>91856</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8389,47 +8389,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>256703</v>
+        <v>2059</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481050</v>
+        <v>480996</v>
       </c>
       <c r="R74" t="n">
-        <v>6784604</v>
+        <v>6784667</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8461,7 +8452,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8471,7 +8462,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8498,7 +8489,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119787848</v>
+        <v>119788514</v>
       </c>
       <c r="B75" t="n">
         <v>91840</v>
@@ -8538,10 +8529,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481187</v>
+        <v>481088</v>
       </c>
       <c r="R75" t="n">
-        <v>6784640</v>
+        <v>6784614</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8588,19 +8579,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119788514</v>
+        <v>119788519</v>
       </c>
       <c r="B76" t="n">
         <v>91840</v>
@@ -8640,10 +8631,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481088</v>
+        <v>481087</v>
       </c>
       <c r="R76" t="n">
-        <v>6784614</v>
+        <v>6784724</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8690,19 +8681,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119788519</v>
+        <v>119787848</v>
       </c>
       <c r="B77" t="n">
         <v>91840</v>
@@ -8742,10 +8733,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481087</v>
+        <v>481187</v>
       </c>
       <c r="R77" t="n">
-        <v>6784724</v>
+        <v>6784640</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8804,10 +8795,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119789066</v>
+        <v>119788550</v>
       </c>
       <c r="B78" t="n">
-        <v>91856</v>
+        <v>90067</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8816,38 +8807,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>480996</v>
+        <v>481050</v>
       </c>
       <c r="R78" t="n">
-        <v>6784667</v>
+        <v>6784604</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9436,10 +9436,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788846</v>
+        <v>119787771</v>
       </c>
       <c r="B84" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9452,21 +9452,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481139</v>
+        <v>481276</v>
       </c>
       <c r="R84" t="n">
-        <v>6784744</v>
+        <v>6784646</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9526,22 +9526,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788851</v>
+        <v>119788928</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9550,38 +9550,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481136</v>
+        <v>481138</v>
       </c>
       <c r="R85" t="n">
-        <v>6784750</v>
+        <v>6784747</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,19 +9611,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9638,22 +9628,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119787715</v>
+        <v>119788846</v>
       </c>
       <c r="B86" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9666,21 +9656,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9690,10 +9680,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481274</v>
+        <v>481139</v>
       </c>
       <c r="R86" t="n">
-        <v>6784652</v>
+        <v>6784744</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9752,10 +9742,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119787771</v>
+        <v>119788851</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9764,38 +9754,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481276</v>
+        <v>481136</v>
       </c>
       <c r="R87" t="n">
-        <v>6784646</v>
+        <v>6784750</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9825,9 +9815,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9842,22 +9842,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119788928</v>
+        <v>119787715</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9870,21 +9870,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481138</v>
+        <v>481274</v>
       </c>
       <c r="R88" t="n">
-        <v>6784747</v>
+        <v>6784652</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9944,12 +9944,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -2987,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706741</v>
+        <v>119706870</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2999,28 +2999,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3030,10 +3034,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481017</v>
+        <v>481067</v>
       </c>
       <c r="R23" t="n">
-        <v>6784518</v>
+        <v>6784504</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3093,10 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706870</v>
+        <v>119706741</v>
       </c>
       <c r="B24" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3105,32 +3109,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481067</v>
+        <v>481017</v>
       </c>
       <c r="R24" t="n">
-        <v>6784504</v>
+        <v>6784518</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119786836</v>
+        <v>119789434</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,34 +6387,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481049</v>
+        <v>481002</v>
       </c>
       <c r="R55" t="n">
-        <v>6784514</v>
+        <v>6784693</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,9 +6449,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,19 +6476,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119787021</v>
+        <v>119786836</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6513,10 +6528,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481048</v>
+        <v>481049</v>
       </c>
       <c r="R56" t="n">
-        <v>6784513</v>
+        <v>6784514</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6563,22 +6578,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119789434</v>
+        <v>119787021</v>
       </c>
       <c r="B57" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6591,39 +6606,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481002</v>
+        <v>481048</v>
       </c>
       <c r="R57" t="n">
-        <v>6784693</v>
+        <v>6784513</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6653,19 +6663,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,12 +6680,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -8916,10 +8916,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788935</v>
+        <v>119788305</v>
       </c>
       <c r="B79" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8932,37 +8932,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480987</v>
+        <v>481083</v>
       </c>
       <c r="R79" t="n">
-        <v>6784663</v>
+        <v>6784643</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8989,9 +8989,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9006,22 +9016,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119787644</v>
+        <v>119788935</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9034,21 +9044,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9058,10 +9068,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481277</v>
+        <v>480987</v>
       </c>
       <c r="R80" t="n">
-        <v>6784621</v>
+        <v>6784663</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9108,12 +9118,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9222,10 +9232,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119788305</v>
+        <v>119787644</v>
       </c>
       <c r="B82" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9238,37 +9248,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481083</v>
+        <v>481277</v>
       </c>
       <c r="R82" t="n">
-        <v>6784643</v>
+        <v>6784621</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9295,19 +9305,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9322,12 +9322,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119787771</v>
+        <v>119788846</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9452,21 +9452,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481276</v>
+        <v>481139</v>
       </c>
       <c r="R84" t="n">
-        <v>6784646</v>
+        <v>6784744</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9526,22 +9526,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788928</v>
+        <v>119788851</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9550,38 +9550,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481138</v>
+        <v>481136</v>
       </c>
       <c r="R85" t="n">
-        <v>6784747</v>
+        <v>6784750</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,9 +9611,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9628,22 +9638,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788846</v>
+        <v>119787715</v>
       </c>
       <c r="B86" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9656,21 +9666,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9680,10 +9690,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481139</v>
+        <v>481274</v>
       </c>
       <c r="R86" t="n">
-        <v>6784744</v>
+        <v>6784652</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,10 +9752,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788851</v>
+        <v>119787771</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9754,38 +9764,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481136</v>
+        <v>481276</v>
       </c>
       <c r="R87" t="n">
-        <v>6784750</v>
+        <v>6784646</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9815,19 +9825,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9842,22 +9842,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119787715</v>
+        <v>119788928</v>
       </c>
       <c r="B88" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9870,21 +9870,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481274</v>
+        <v>481138</v>
       </c>
       <c r="R88" t="n">
-        <v>6784652</v>
+        <v>6784747</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9944,12 +9944,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -2987,10 +2987,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119706870</v>
+        <v>119706741</v>
       </c>
       <c r="B23" t="n">
-        <v>89252</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2999,32 +2999,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3034,10 +3030,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>481067</v>
+        <v>481017</v>
       </c>
       <c r="R23" t="n">
-        <v>6784504</v>
+        <v>6784518</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3097,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119706741</v>
+        <v>119706870</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>89252</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3109,28 +3105,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>481017</v>
+        <v>481067</v>
       </c>
       <c r="R24" t="n">
-        <v>6784518</v>
+        <v>6784504</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119789434</v>
+        <v>119786836</v>
       </c>
       <c r="B55" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,39 +6387,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481002</v>
+        <v>481049</v>
       </c>
       <c r="R55" t="n">
-        <v>6784693</v>
+        <v>6784514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6449,19 +6444,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6476,19 +6461,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119786836</v>
+        <v>119787021</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6528,10 +6513,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481049</v>
+        <v>481048</v>
       </c>
       <c r="R56" t="n">
-        <v>6784514</v>
+        <v>6784513</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6578,22 +6563,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119787021</v>
+        <v>119789434</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6606,34 +6591,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481048</v>
+        <v>481002</v>
       </c>
       <c r="R57" t="n">
-        <v>6784513</v>
+        <v>6784693</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6663,9 +6653,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6680,12 +6680,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7434,10 +7434,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119787770</v>
+        <v>119787681</v>
       </c>
       <c r="B65" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7450,34 +7450,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481267</v>
+        <v>481294</v>
       </c>
       <c r="R65" t="n">
-        <v>6784656</v>
+        <v>6784626</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7507,19 +7507,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7534,22 +7524,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119787681</v>
+        <v>119787770</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>91856</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7562,34 +7552,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481294</v>
+        <v>481267</v>
       </c>
       <c r="R66" t="n">
-        <v>6784626</v>
+        <v>6784656</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7619,9 +7609,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7636,12 +7636,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8071,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119788482</v>
+        <v>119789001</v>
       </c>
       <c r="B71" t="n">
-        <v>89275</v>
+        <v>91856</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8083,25 +8083,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481092</v>
+        <v>481138</v>
       </c>
       <c r="R71" t="n">
-        <v>6784610</v>
+        <v>6784747</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,22 +8161,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119789001</v>
+        <v>119787935</v>
       </c>
       <c r="B72" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8189,21 +8189,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481138</v>
+        <v>481160</v>
       </c>
       <c r="R72" t="n">
-        <v>6784747</v>
+        <v>6784611</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8275,10 +8275,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119787935</v>
+        <v>119788482</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>89275</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8287,25 +8287,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8315,10 +8315,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481160</v>
+        <v>481092</v>
       </c>
       <c r="R73" t="n">
-        <v>6784611</v>
+        <v>6784610</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8365,12 +8365,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8916,10 +8916,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788305</v>
+        <v>119788935</v>
       </c>
       <c r="B79" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8932,37 +8932,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481083</v>
+        <v>480987</v>
       </c>
       <c r="R79" t="n">
-        <v>6784643</v>
+        <v>6784663</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8989,19 +8989,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9016,22 +9006,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119788935</v>
+        <v>119787644</v>
       </c>
       <c r="B80" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9044,21 +9034,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9068,10 +9058,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>480987</v>
+        <v>481277</v>
       </c>
       <c r="R80" t="n">
-        <v>6784663</v>
+        <v>6784621</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9118,12 +9108,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9232,10 +9222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119787644</v>
+        <v>119788305</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9248,37 +9238,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481277</v>
+        <v>481083</v>
       </c>
       <c r="R82" t="n">
-        <v>6784621</v>
+        <v>6784643</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9305,9 +9295,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9322,12 +9322,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9436,10 +9436,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788846</v>
+        <v>119787771</v>
       </c>
       <c r="B84" t="n">
-        <v>91832</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9452,21 +9452,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9476,10 +9476,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481139</v>
+        <v>481276</v>
       </c>
       <c r="R84" t="n">
-        <v>6784744</v>
+        <v>6784646</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9526,22 +9526,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788851</v>
+        <v>119788928</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9550,38 +9550,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481136</v>
+        <v>481138</v>
       </c>
       <c r="R85" t="n">
-        <v>6784750</v>
+        <v>6784747</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,19 +9611,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9638,22 +9628,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119787715</v>
+        <v>119788846</v>
       </c>
       <c r="B86" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9666,21 +9656,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9690,10 +9680,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481274</v>
+        <v>481139</v>
       </c>
       <c r="R86" t="n">
-        <v>6784652</v>
+        <v>6784744</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9752,10 +9742,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119787771</v>
+        <v>119788851</v>
       </c>
       <c r="B87" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9764,38 +9754,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481276</v>
+        <v>481136</v>
       </c>
       <c r="R87" t="n">
-        <v>6784646</v>
+        <v>6784750</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9825,9 +9815,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9842,22 +9842,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119788928</v>
+        <v>119787715</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9870,21 +9870,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481138</v>
+        <v>481274</v>
       </c>
       <c r="R88" t="n">
-        <v>6784747</v>
+        <v>6784652</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9944,12 +9944,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -3309,10 +3309,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119741905</v>
+        <v>119741440</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>89269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3321,25 +3321,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,7 +3355,7 @@
         <v>6784535</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3421,10 +3421,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119741440</v>
+        <v>119741905</v>
       </c>
       <c r="B27" t="n">
-        <v>89252</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3433,25 +3433,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
         <v>6784535</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119789105</v>
+        <v>119787790</v>
       </c>
       <c r="B28" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481038</v>
+        <v>481260</v>
       </c>
       <c r="R28" t="n">
-        <v>6784721</v>
+        <v>6784612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788082</v>
+        <v>119788715</v>
       </c>
       <c r="B29" t="n">
-        <v>91856</v>
+        <v>91874</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3671,14 +3671,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481144</v>
+        <v>481104</v>
       </c>
       <c r="R29" t="n">
-        <v>6784602</v>
+        <v>6784681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,9 +3708,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3725,22 +3735,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119787665</v>
+        <v>119787681</v>
       </c>
       <c r="B30" t="n">
-        <v>91856</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3753,21 +3763,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3777,10 +3787,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481287</v>
+        <v>481294</v>
       </c>
       <c r="R30" t="n">
-        <v>6784633</v>
+        <v>6784626</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3839,10 +3849,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119787833</v>
+        <v>119789074</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3851,38 +3861,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481250</v>
+        <v>481031</v>
       </c>
       <c r="R31" t="n">
-        <v>6784659</v>
+        <v>6784712</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,19 +3922,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3939,22 +3939,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119787807</v>
+        <v>119788851</v>
       </c>
       <c r="B32" t="n">
-        <v>91856</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3963,25 +3963,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481250</v>
+        <v>481136</v>
       </c>
       <c r="R32" t="n">
-        <v>6784659</v>
+        <v>6784750</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4063,10 +4063,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119789064</v>
+        <v>119787807</v>
       </c>
       <c r="B33" t="n">
-        <v>91884</v>
+        <v>91874</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4079,34 +4079,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481010</v>
+        <v>481250</v>
       </c>
       <c r="R33" t="n">
-        <v>6784679</v>
+        <v>6784659</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,9 +4136,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,22 +4163,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119786882</v>
+        <v>119788550</v>
       </c>
       <c r="B34" t="n">
-        <v>91856</v>
+        <v>90084</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4177,38 +4187,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>256703</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481048</v>
+        <v>481050</v>
       </c>
       <c r="R34" t="n">
-        <v>6784513</v>
+        <v>6784604</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4238,9 +4257,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4255,22 +4284,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119789077</v>
+        <v>119787848</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4279,25 +4308,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4307,10 +4336,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481052</v>
+        <v>481187</v>
       </c>
       <c r="R35" t="n">
-        <v>6784759</v>
+        <v>6784640</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4357,22 +4386,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119787790</v>
+        <v>119788846</v>
       </c>
       <c r="B36" t="n">
-        <v>91834</v>
+        <v>91850</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4385,21 +4414,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4409,10 +4438,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481260</v>
+        <v>481139</v>
       </c>
       <c r="R36" t="n">
-        <v>6784612</v>
+        <v>6784744</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4471,10 +4500,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119787470</v>
+        <v>119788482</v>
       </c>
       <c r="B37" t="n">
-        <v>91821</v>
+        <v>89292</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4487,21 +4516,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6055</v>
+        <v>6286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4511,10 +4540,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481284</v>
+        <v>481092</v>
       </c>
       <c r="R37" t="n">
-        <v>6784549</v>
+        <v>6784610</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,10 +4602,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119787115</v>
+        <v>119788571</v>
       </c>
       <c r="B38" t="n">
-        <v>91856</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4589,21 +4618,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4613,10 +4642,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481178</v>
+        <v>481088</v>
       </c>
       <c r="R38" t="n">
-        <v>6784510</v>
+        <v>6784614</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4663,22 +4692,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119789016</v>
+        <v>119787825</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4687,38 +4716,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480995</v>
+        <v>481250</v>
       </c>
       <c r="R39" t="n">
-        <v>6784692</v>
+        <v>6784659</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4748,9 +4777,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4765,22 +4804,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119787759</v>
+        <v>119787544</v>
       </c>
       <c r="B40" t="n">
-        <v>79144</v>
+        <v>8432</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4789,38 +4828,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481248</v>
+        <v>481291</v>
       </c>
       <c r="R40" t="n">
-        <v>6784628</v>
+        <v>6784590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4850,39 +4898,50 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119788786</v>
+        <v>119787774</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>91902</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4895,21 +4954,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4919,10 +4978,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481176</v>
+        <v>481250</v>
       </c>
       <c r="R41" t="n">
-        <v>6784737</v>
+        <v>6784627</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4969,22 +5028,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119788908</v>
+        <v>119788662</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4993,25 +5052,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5021,10 +5080,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481028</v>
+        <v>481133</v>
       </c>
       <c r="R42" t="n">
-        <v>6784697</v>
+        <v>6784731</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5083,10 +5142,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119788104</v>
+        <v>119788935</v>
       </c>
       <c r="B43" t="n">
-        <v>8432</v>
+        <v>91874</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5095,43 +5154,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>481122</v>
+        <v>480987</v>
       </c>
       <c r="R43" t="n">
-        <v>6784602</v>
+        <v>6784663</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5190,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119787764</v>
+        <v>119787470</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>91839</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5202,25 +5256,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6055</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5230,10 +5284,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481252</v>
+        <v>481284</v>
       </c>
       <c r="R44" t="n">
-        <v>6784627</v>
+        <v>6784549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,10 +5346,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119788782</v>
+        <v>119787021</v>
       </c>
       <c r="B45" t="n">
-        <v>91863</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5308,43 +5362,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481195</v>
+        <v>481048</v>
       </c>
       <c r="R45" t="n">
-        <v>6784739</v>
+        <v>6784513</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5374,19 +5419,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5401,22 +5436,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788776</v>
+        <v>119788574</v>
       </c>
       <c r="B46" t="n">
-        <v>91856</v>
+        <v>8432</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5425,38 +5460,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481179</v>
+        <v>481104</v>
       </c>
       <c r="R46" t="n">
-        <v>6784744</v>
+        <v>6784681</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5486,9 +5526,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5503,22 +5553,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119787028</v>
+        <v>119788104</v>
       </c>
       <c r="B47" t="n">
-        <v>91856</v>
+        <v>8432</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5527,38 +5577,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481150</v>
+        <v>481122</v>
       </c>
       <c r="R47" t="n">
-        <v>6784524</v>
+        <v>6784602</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5617,10 +5672,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119788565</v>
+        <v>119787028</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5629,25 +5684,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5657,10 +5712,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481108</v>
+        <v>481150</v>
       </c>
       <c r="R48" t="n">
-        <v>6784708</v>
+        <v>6784524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5719,10 +5774,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788094</v>
+        <v>119788519</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5759,10 +5814,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481132</v>
+        <v>481087</v>
       </c>
       <c r="R49" t="n">
-        <v>6784594</v>
+        <v>6784724</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,22 +5864,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119787544</v>
+        <v>119789066</v>
       </c>
       <c r="B50" t="n">
-        <v>8432</v>
+        <v>91874</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5833,47 +5888,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>481291</v>
+        <v>480996</v>
       </c>
       <c r="R50" t="n">
-        <v>6784590</v>
+        <v>6784667</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5905,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5915,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5924,7 +5970,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5943,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119787139</v>
+        <v>119787759</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>79160</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5959,34 +6004,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481215</v>
+        <v>481248</v>
       </c>
       <c r="R51" t="n">
-        <v>6784513</v>
+        <v>6784628</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6016,19 +6061,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6043,22 +6078,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119788312</v>
+        <v>119788908</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6095,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481062</v>
+        <v>481028</v>
       </c>
       <c r="R52" t="n">
-        <v>6784614</v>
+        <v>6784697</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6145,22 +6180,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119788483</v>
+        <v>119787740</v>
       </c>
       <c r="B53" t="n">
-        <v>89275</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6169,38 +6204,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481050</v>
+        <v>481276</v>
       </c>
       <c r="R53" t="n">
-        <v>6784604</v>
+        <v>6784646</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6230,19 +6265,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6257,22 +6282,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119789074</v>
+        <v>119788514</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6309,10 +6334,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481031</v>
+        <v>481088</v>
       </c>
       <c r="R54" t="n">
-        <v>6784712</v>
+        <v>6784614</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6359,22 +6384,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119786836</v>
+        <v>119789105</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>91874</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6387,21 +6412,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6411,10 +6436,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481049</v>
+        <v>481038</v>
       </c>
       <c r="R55" t="n">
-        <v>6784514</v>
+        <v>6784721</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6473,10 +6498,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119787021</v>
+        <v>119787644</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6513,10 +6538,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481048</v>
+        <v>481277</v>
       </c>
       <c r="R56" t="n">
-        <v>6784513</v>
+        <v>6784621</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6575,10 +6600,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119789434</v>
+        <v>119787139</v>
       </c>
       <c r="B57" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6591,39 +6616,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481002</v>
+        <v>481215</v>
       </c>
       <c r="R57" t="n">
-        <v>6784693</v>
+        <v>6784513</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6655,7 +6675,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6665,7 +6685,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6692,10 +6712,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119788774</v>
+        <v>119787764</v>
       </c>
       <c r="B58" t="n">
-        <v>88153</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6708,34 +6728,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4962</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481195</v>
+        <v>481252</v>
       </c>
       <c r="R58" t="n">
-        <v>6784739</v>
+        <v>6784627</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6765,19 +6785,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6792,22 +6802,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119792265</v>
+        <v>119789064</v>
       </c>
       <c r="B59" t="n">
-        <v>89239</v>
+        <v>91902</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6816,48 +6826,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6268</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481044</v>
+        <v>481010</v>
       </c>
       <c r="R59" t="n">
-        <v>6784736</v>
+        <v>6784679</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6895,29 +6898,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119787740</v>
+        <v>119789434</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>57473</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6926,38 +6928,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481276</v>
+        <v>481002</v>
       </c>
       <c r="R60" t="n">
-        <v>6784646</v>
+        <v>6784693</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6987,9 +6994,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7004,22 +7021,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119788715</v>
+        <v>119788766</v>
       </c>
       <c r="B61" t="n">
-        <v>91856</v>
+        <v>78543</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7032,34 +7049,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2059</v>
+        <v>230405</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481104</v>
+        <v>481176</v>
       </c>
       <c r="R61" t="n">
-        <v>6784681</v>
+        <v>6784737</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7089,19 +7106,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7116,22 +7123,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119788560</v>
+        <v>119787827</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7140,25 +7147,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7168,10 +7175,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481088</v>
+        <v>481229</v>
       </c>
       <c r="R62" t="n">
-        <v>6784614</v>
+        <v>6784643</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7218,22 +7225,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119786992</v>
+        <v>119788094</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7270,10 +7277,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481048</v>
+        <v>481132</v>
       </c>
       <c r="R63" t="n">
-        <v>6784513</v>
+        <v>6784594</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7332,10 +7339,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119787002</v>
+        <v>119787744</v>
       </c>
       <c r="B64" t="n">
-        <v>78171</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7348,37 +7355,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481114</v>
+        <v>481267</v>
       </c>
       <c r="R64" t="n">
-        <v>6784523</v>
+        <v>6784656</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7405,9 +7412,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7422,22 +7439,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119787681</v>
+        <v>119789077</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7474,10 +7491,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481294</v>
+        <v>481052</v>
       </c>
       <c r="R65" t="n">
-        <v>6784626</v>
+        <v>6784759</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7524,22 +7541,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119787770</v>
+        <v>119788312</v>
       </c>
       <c r="B66" t="n">
-        <v>91856</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7552,34 +7569,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481267</v>
+        <v>481062</v>
       </c>
       <c r="R66" t="n">
-        <v>6784656</v>
+        <v>6784614</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7609,19 +7626,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7636,22 +7643,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119787774</v>
+        <v>119788483</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>89292</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7660,38 +7667,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481250</v>
+        <v>481050</v>
       </c>
       <c r="R67" t="n">
-        <v>6784627</v>
+        <v>6784604</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7721,9 +7728,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7738,22 +7755,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119787167</v>
+        <v>119788928</v>
       </c>
       <c r="B68" t="n">
-        <v>91856</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7766,21 +7783,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7790,10 +7807,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>481197</v>
+        <v>481138</v>
       </c>
       <c r="R68" t="n">
-        <v>6784509</v>
+        <v>6784747</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7840,22 +7857,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119788574</v>
+        <v>119788950</v>
       </c>
       <c r="B69" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7868,39 +7885,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481104</v>
+        <v>480996</v>
       </c>
       <c r="R69" t="n">
-        <v>6784681</v>
+        <v>6784667</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7932,7 +7944,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7942,7 +7954,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,10 +7981,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119787827</v>
+        <v>119787770</v>
       </c>
       <c r="B70" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7981,38 +7993,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481229</v>
+        <v>481267</v>
       </c>
       <c r="R70" t="n">
-        <v>6784643</v>
+        <v>6784656</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8042,9 +8054,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8059,22 +8081,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119789001</v>
+        <v>119787115</v>
       </c>
       <c r="B71" t="n">
-        <v>91856</v>
+        <v>91874</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8111,10 +8133,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481138</v>
+        <v>481178</v>
       </c>
       <c r="R71" t="n">
-        <v>6784747</v>
+        <v>6784510</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8161,22 +8183,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119787935</v>
+        <v>119788774</v>
       </c>
       <c r="B72" t="n">
-        <v>78526</v>
+        <v>88170</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8189,34 +8211,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>4962</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481160</v>
+        <v>481195</v>
       </c>
       <c r="R72" t="n">
-        <v>6784611</v>
+        <v>6784739</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8246,9 +8268,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8263,22 +8295,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119788482</v>
+        <v>119789016</v>
       </c>
       <c r="B73" t="n">
-        <v>89275</v>
+        <v>91858</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8287,25 +8319,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8315,10 +8347,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>481092</v>
+        <v>480995</v>
       </c>
       <c r="R73" t="n">
-        <v>6784610</v>
+        <v>6784692</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8377,10 +8409,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119789066</v>
+        <v>119786992</v>
       </c>
       <c r="B74" t="n">
-        <v>91856</v>
+        <v>91858</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8389,38 +8421,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480996</v>
+        <v>481048</v>
       </c>
       <c r="R74" t="n">
-        <v>6784667</v>
+        <v>6784513</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8450,19 +8482,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8477,22 +8499,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119788514</v>
+        <v>119792265</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>89256</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8505,37 +8527,44 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6268</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481088</v>
+        <v>481044</v>
       </c>
       <c r="R75" t="n">
-        <v>6784614</v>
+        <v>6784736</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8573,28 +8602,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119788519</v>
+        <v>119787167</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8603,25 +8633,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8631,10 +8661,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481087</v>
+        <v>481197</v>
       </c>
       <c r="R76" t="n">
-        <v>6784724</v>
+        <v>6784509</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8693,10 +8723,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119787848</v>
+        <v>119788082</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8705,25 +8735,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8733,10 +8763,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481187</v>
+        <v>481144</v>
       </c>
       <c r="R77" t="n">
-        <v>6784640</v>
+        <v>6784602</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8795,10 +8825,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119788550</v>
+        <v>119789001</v>
       </c>
       <c r="B78" t="n">
-        <v>90067</v>
+        <v>91874</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8807,47 +8837,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>256703</v>
+        <v>2059</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481050</v>
+        <v>481138</v>
       </c>
       <c r="R78" t="n">
-        <v>6784604</v>
+        <v>6784747</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8877,19 +8898,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8904,22 +8915,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119788935</v>
+        <v>119787771</v>
       </c>
       <c r="B79" t="n">
-        <v>91856</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8932,21 +8943,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8956,10 +8967,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>480987</v>
+        <v>481276</v>
       </c>
       <c r="R79" t="n">
-        <v>6784663</v>
+        <v>6784646</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9006,22 +9017,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119787644</v>
+        <v>119787094</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9030,25 +9041,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9058,10 +9069,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481277</v>
+        <v>481175</v>
       </c>
       <c r="R80" t="n">
-        <v>6784621</v>
+        <v>6784516</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9108,22 +9119,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119788662</v>
+        <v>119787715</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9132,25 +9143,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9160,10 +9171,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481133</v>
+        <v>481274</v>
       </c>
       <c r="R81" t="n">
-        <v>6784731</v>
+        <v>6784652</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9222,10 +9233,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119788305</v>
+        <v>119786882</v>
       </c>
       <c r="B82" t="n">
-        <v>91884</v>
+        <v>91874</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9238,37 +9249,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481083</v>
+        <v>481048</v>
       </c>
       <c r="R82" t="n">
-        <v>6784643</v>
+        <v>6784513</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9295,19 +9306,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9322,22 +9323,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119788033</v>
+        <v>119788776</v>
       </c>
       <c r="B83" t="n">
-        <v>91856</v>
+        <v>91874</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9374,10 +9375,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481181</v>
+        <v>481179</v>
       </c>
       <c r="R83" t="n">
-        <v>6784644</v>
+        <v>6784744</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9436,10 +9437,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119787771</v>
+        <v>119788782</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>91881</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9452,34 +9453,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481276</v>
+        <v>481195</v>
       </c>
       <c r="R84" t="n">
-        <v>6784646</v>
+        <v>6784739</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9509,9 +9519,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9526,22 +9546,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119788928</v>
+        <v>119786836</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9578,10 +9598,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481138</v>
+        <v>481049</v>
       </c>
       <c r="R85" t="n">
-        <v>6784747</v>
+        <v>6784514</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9628,22 +9648,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788846</v>
+        <v>119788305</v>
       </c>
       <c r="B86" t="n">
-        <v>91832</v>
+        <v>91902</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9656,37 +9676,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481139</v>
+        <v>481083</v>
       </c>
       <c r="R86" t="n">
-        <v>6784744</v>
+        <v>6784643</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9713,9 +9733,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9730,22 +9760,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119788851</v>
+        <v>119787665</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>91874</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9754,38 +9784,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481136</v>
+        <v>481287</v>
       </c>
       <c r="R87" t="n">
-        <v>6784750</v>
+        <v>6784633</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9815,19 +9845,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9842,22 +9862,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119787715</v>
+        <v>119787935</v>
       </c>
       <c r="B88" t="n">
-        <v>91884</v>
+        <v>78542</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9870,21 +9890,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9894,10 +9914,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481274</v>
+        <v>481160</v>
       </c>
       <c r="R88" t="n">
-        <v>6784652</v>
+        <v>6784611</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9944,22 +9964,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119787744</v>
+        <v>119788033</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>91874</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9972,37 +9992,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481267</v>
+        <v>481181</v>
       </c>
       <c r="R89" t="n">
-        <v>6784656</v>
+        <v>6784644</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10029,19 +10049,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10056,22 +10066,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119787094</v>
+        <v>119787002</v>
       </c>
       <c r="B90" t="n">
-        <v>91840</v>
+        <v>78187</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10080,25 +10090,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10108,10 +10118,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481175</v>
+        <v>481114</v>
       </c>
       <c r="R90" t="n">
-        <v>6784516</v>
+        <v>6784523</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10170,10 +10180,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119788950</v>
+        <v>119788565</v>
       </c>
       <c r="B91" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10206,14 +10216,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>480996</v>
+        <v>481108</v>
       </c>
       <c r="R91" t="n">
-        <v>6784667</v>
+        <v>6784708</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10243,19 +10253,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10270,12 +10270,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -3533,10 +3533,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119787790</v>
+        <v>119787665</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>481260</v>
+        <v>481287</v>
       </c>
       <c r="R28" t="n">
-        <v>6784612</v>
+        <v>6784633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119788715</v>
+        <v>119788483</v>
       </c>
       <c r="B29" t="n">
-        <v>91874</v>
+        <v>89292</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3647,25 +3647,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>481104</v>
+        <v>481050</v>
       </c>
       <c r="R29" t="n">
-        <v>6784681</v>
+        <v>6784604</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3747,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119787681</v>
+        <v>119787827</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3759,25 +3759,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>481294</v>
+        <v>481229</v>
       </c>
       <c r="R30" t="n">
-        <v>6784626</v>
+        <v>6784643</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3849,7 +3849,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119789074</v>
+        <v>119788514</v>
       </c>
       <c r="B31" t="n">
         <v>91858</v>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>481031</v>
+        <v>481088</v>
       </c>
       <c r="R31" t="n">
-        <v>6784712</v>
+        <v>6784614</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3939,22 +3939,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119788851</v>
+        <v>119787167</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3963,38 +3963,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>481136</v>
+        <v>481197</v>
       </c>
       <c r="R32" t="n">
-        <v>6784750</v>
+        <v>6784509</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4024,19 +4024,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,19 +4041,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119787807</v>
+        <v>119788935</v>
       </c>
       <c r="B33" t="n">
         <v>91874</v>
@@ -4099,14 +4089,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>481250</v>
+        <v>480987</v>
       </c>
       <c r="R33" t="n">
-        <v>6784659</v>
+        <v>6784663</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4136,19 +4126,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4163,22 +4143,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119788550</v>
+        <v>119789434</v>
       </c>
       <c r="B34" t="n">
-        <v>90084</v>
+        <v>57473</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4187,35 +4167,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>256703</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4224,10 +4200,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>481050</v>
+        <v>481002</v>
       </c>
       <c r="R34" t="n">
-        <v>6784604</v>
+        <v>6784693</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4259,7 +4235,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4269,7 +4245,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4296,10 +4272,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119787848</v>
+        <v>119787115</v>
       </c>
       <c r="B35" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4308,25 +4284,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4336,10 +4312,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>481187</v>
+        <v>481178</v>
       </c>
       <c r="R35" t="n">
-        <v>6784640</v>
+        <v>6784510</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4398,10 +4374,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119788846</v>
+        <v>119787831</v>
       </c>
       <c r="B36" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4414,34 +4390,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>481139</v>
+        <v>481250</v>
       </c>
       <c r="R36" t="n">
-        <v>6784744</v>
+        <v>6784659</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4471,9 +4447,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,22 +4474,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119788482</v>
+        <v>119788715</v>
       </c>
       <c r="B37" t="n">
-        <v>89292</v>
+        <v>91874</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4512,38 +4498,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>481092</v>
+        <v>481104</v>
       </c>
       <c r="R37" t="n">
-        <v>6784610</v>
+        <v>6784681</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4573,9 +4559,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4590,19 +4586,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119788571</v>
+        <v>119787644</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -4642,10 +4638,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>481088</v>
+        <v>481277</v>
       </c>
       <c r="R38" t="n">
-        <v>6784614</v>
+        <v>6784621</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4704,7 +4700,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119787825</v>
+        <v>119788928</v>
       </c>
       <c r="B39" t="n">
         <v>78542</v>
@@ -4740,14 +4736,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>481250</v>
+        <v>481138</v>
       </c>
       <c r="R39" t="n">
-        <v>6784659</v>
+        <v>6784747</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4777,19 +4773,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4804,22 +4790,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119787544</v>
+        <v>119789016</v>
       </c>
       <c r="B40" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4832,43 +4818,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>481291</v>
+        <v>480995</v>
       </c>
       <c r="R40" t="n">
-        <v>6784590</v>
+        <v>6784692</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4898,50 +4875,39 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119787774</v>
+        <v>119788094</v>
       </c>
       <c r="B41" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4950,25 +4916,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4978,10 +4944,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>481250</v>
+        <v>481132</v>
       </c>
       <c r="R41" t="n">
-        <v>6784627</v>
+        <v>6784594</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5028,22 +4994,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119788662</v>
+        <v>119787470</v>
       </c>
       <c r="B42" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5052,25 +5018,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5080,10 +5046,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>481133</v>
+        <v>481284</v>
       </c>
       <c r="R42" t="n">
-        <v>6784731</v>
+        <v>6784549</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5142,10 +5108,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119788935</v>
+        <v>119789064</v>
       </c>
       <c r="B43" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5158,21 +5124,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5182,10 +5148,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480987</v>
+        <v>481010</v>
       </c>
       <c r="R43" t="n">
-        <v>6784663</v>
+        <v>6784679</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5244,10 +5210,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119787470</v>
+        <v>119788782</v>
       </c>
       <c r="B44" t="n">
-        <v>91839</v>
+        <v>91881</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5256,38 +5222,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481284</v>
+        <v>481195</v>
       </c>
       <c r="R44" t="n">
-        <v>6784549</v>
+        <v>6784739</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5317,9 +5292,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5334,22 +5319,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119787021</v>
+        <v>119788305</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5362,37 +5347,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481048</v>
+        <v>481083</v>
       </c>
       <c r="R45" t="n">
-        <v>6784513</v>
+        <v>6784643</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5419,9 +5404,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5436,22 +5431,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788574</v>
+        <v>119788766</v>
       </c>
       <c r="B46" t="n">
-        <v>8432</v>
+        <v>78543</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5460,43 +5455,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481104</v>
+        <v>481176</v>
       </c>
       <c r="R46" t="n">
-        <v>6784681</v>
+        <v>6784737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5526,19 +5516,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,22 +5533,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119788104</v>
+        <v>119786882</v>
       </c>
       <c r="B47" t="n">
-        <v>8432</v>
+        <v>91874</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5577,43 +5557,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481122</v>
+        <v>481048</v>
       </c>
       <c r="R47" t="n">
-        <v>6784602</v>
+        <v>6784513</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5660,22 +5635,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119787028</v>
+        <v>119788950</v>
       </c>
       <c r="B48" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5684,38 +5659,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>481150</v>
+        <v>480996</v>
       </c>
       <c r="R48" t="n">
-        <v>6784524</v>
+        <v>6784667</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5745,9 +5720,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5762,22 +5747,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119788519</v>
+        <v>119788574</v>
       </c>
       <c r="B49" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5790,34 +5775,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>481087</v>
+        <v>481104</v>
       </c>
       <c r="R49" t="n">
-        <v>6784724</v>
+        <v>6784681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5847,9 +5837,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5864,22 +5864,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119789066</v>
+        <v>119787681</v>
       </c>
       <c r="B50" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5892,34 +5892,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480996</v>
+        <v>481294</v>
       </c>
       <c r="R50" t="n">
-        <v>6784667</v>
+        <v>6784626</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,19 +5949,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5976,22 +5966,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119787759</v>
+        <v>119788662</v>
       </c>
       <c r="B51" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6000,25 +5990,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6028,10 +6018,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>481248</v>
+        <v>481133</v>
       </c>
       <c r="R51" t="n">
-        <v>6784628</v>
+        <v>6784731</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6090,10 +6080,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119788908</v>
+        <v>119788846</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>91850</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6106,21 +6096,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6130,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>481028</v>
+        <v>481139</v>
       </c>
       <c r="R52" t="n">
-        <v>6784697</v>
+        <v>6784744</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6192,7 +6182,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119787740</v>
+        <v>119788851</v>
       </c>
       <c r="B53" t="n">
         <v>91858</v>
@@ -6228,14 +6218,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>481276</v>
+        <v>481136</v>
       </c>
       <c r="R53" t="n">
-        <v>6784646</v>
+        <v>6784750</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6265,9 +6255,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6282,22 +6282,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119788514</v>
+        <v>119787770</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6306,38 +6306,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>481088</v>
+        <v>481267</v>
       </c>
       <c r="R54" t="n">
-        <v>6784614</v>
+        <v>6784656</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6367,9 +6367,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6384,22 +6394,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119789105</v>
+        <v>119787139</v>
       </c>
       <c r="B55" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6412,34 +6422,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>481038</v>
+        <v>481215</v>
       </c>
       <c r="R55" t="n">
-        <v>6784721</v>
+        <v>6784513</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6469,9 +6479,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6486,19 +6506,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119787644</v>
+        <v>119788571</v>
       </c>
       <c r="B56" t="n">
         <v>78542</v>
@@ -6538,10 +6558,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>481277</v>
+        <v>481088</v>
       </c>
       <c r="R56" t="n">
-        <v>6784621</v>
+        <v>6784614</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6600,7 +6620,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119787139</v>
+        <v>119787744</v>
       </c>
       <c r="B57" t="n">
         <v>78542</v>
@@ -6640,13 +6660,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>481215</v>
+        <v>481267</v>
       </c>
       <c r="R57" t="n">
-        <v>6784513</v>
+        <v>6784656</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6675,7 +6695,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6685,7 +6705,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6712,10 +6732,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119787764</v>
+        <v>119789074</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6724,25 +6744,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6752,10 +6772,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>481252</v>
+        <v>481031</v>
       </c>
       <c r="R58" t="n">
-        <v>6784627</v>
+        <v>6784712</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6814,10 +6834,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119789064</v>
+        <v>119787759</v>
       </c>
       <c r="B59" t="n">
-        <v>91902</v>
+        <v>79160</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6830,21 +6850,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6854,10 +6874,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>481010</v>
+        <v>481248</v>
       </c>
       <c r="R59" t="n">
-        <v>6784679</v>
+        <v>6784628</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6916,10 +6936,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119789434</v>
+        <v>119788312</v>
       </c>
       <c r="B60" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6932,39 +6952,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>481002</v>
+        <v>481062</v>
       </c>
       <c r="R60" t="n">
-        <v>6784693</v>
+        <v>6784614</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6994,19 +7009,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7021,22 +7026,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119788766</v>
+        <v>119787764</v>
       </c>
       <c r="B61" t="n">
-        <v>78543</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7049,16 +7054,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7073,10 +7078,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>481176</v>
+        <v>481252</v>
       </c>
       <c r="R61" t="n">
-        <v>6784737</v>
+        <v>6784627</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7123,19 +7128,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119787827</v>
+        <v>119786992</v>
       </c>
       <c r="B62" t="n">
         <v>91858</v>
@@ -7175,10 +7180,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>481229</v>
+        <v>481048</v>
       </c>
       <c r="R62" t="n">
-        <v>6784643</v>
+        <v>6784513</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7225,22 +7230,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119788094</v>
+        <v>119787028</v>
       </c>
       <c r="B63" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7249,25 +7254,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7277,10 +7282,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>481132</v>
+        <v>481150</v>
       </c>
       <c r="R63" t="n">
-        <v>6784594</v>
+        <v>6784524</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7327,22 +7332,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119787744</v>
+        <v>119789066</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>91874</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7355,21 +7360,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7379,13 +7384,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>481267</v>
+        <v>480996</v>
       </c>
       <c r="R64" t="n">
-        <v>6784656</v>
+        <v>6784667</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7414,7 +7419,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7424,7 +7429,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7451,7 +7456,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119789077</v>
+        <v>119787833</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -7487,14 +7492,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>481052</v>
+        <v>481250</v>
       </c>
       <c r="R65" t="n">
-        <v>6784759</v>
+        <v>6784659</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7524,9 +7529,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7541,22 +7556,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119788312</v>
+        <v>119787774</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>91902</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7569,21 +7584,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7593,10 +7608,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>481062</v>
+        <v>481250</v>
       </c>
       <c r="R66" t="n">
-        <v>6784614</v>
+        <v>6784627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7643,22 +7658,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119788483</v>
+        <v>119787544</v>
       </c>
       <c r="B67" t="n">
-        <v>89292</v>
+        <v>8432</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7667,38 +7682,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6286</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481050</v>
+        <v>481291</v>
       </c>
       <c r="R67" t="n">
-        <v>6784604</v>
+        <v>6784590</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7730,7 +7754,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7740,7 +7764,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7749,6 +7773,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7767,10 +7792,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119788928</v>
+        <v>119788033</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>91874</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7783,21 +7808,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7807,10 +7832,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>481138</v>
+        <v>481181</v>
       </c>
       <c r="R68" t="n">
-        <v>6784747</v>
+        <v>6784644</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7857,22 +7882,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119788950</v>
+        <v>119786836</v>
       </c>
       <c r="B69" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7881,38 +7906,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480996</v>
+        <v>481049</v>
       </c>
       <c r="R69" t="n">
-        <v>6784667</v>
+        <v>6784514</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7942,19 +7967,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7969,19 +7984,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119787770</v>
+        <v>119788776</v>
       </c>
       <c r="B70" t="n">
         <v>91874</v>
@@ -8017,14 +8032,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481267</v>
+        <v>481179</v>
       </c>
       <c r="R70" t="n">
-        <v>6784656</v>
+        <v>6784744</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8054,19 +8069,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8081,19 +8086,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119787115</v>
+        <v>119789105</v>
       </c>
       <c r="B71" t="n">
         <v>91874</v>
@@ -8133,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481178</v>
+        <v>481038</v>
       </c>
       <c r="R71" t="n">
-        <v>6784510</v>
+        <v>6784721</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8195,10 +8200,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119788774</v>
+        <v>119792265</v>
       </c>
       <c r="B72" t="n">
-        <v>88170</v>
+        <v>89256</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8207,41 +8212,48 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4962</v>
+        <v>6268</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Kumm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>481195</v>
+        <v>481044</v>
       </c>
       <c r="R72" t="n">
-        <v>6784739</v>
+        <v>6784736</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8268,27 +8280,18 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8307,10 +8310,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119789016</v>
+        <v>119787935</v>
       </c>
       <c r="B73" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8319,25 +8322,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8347,10 +8350,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480995</v>
+        <v>481160</v>
       </c>
       <c r="R73" t="n">
-        <v>6784692</v>
+        <v>6784611</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8397,22 +8400,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119786992</v>
+        <v>119787771</v>
       </c>
       <c r="B74" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8421,25 +8424,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8449,10 +8452,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>481048</v>
+        <v>481276</v>
       </c>
       <c r="R74" t="n">
-        <v>6784513</v>
+        <v>6784646</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8511,10 +8514,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119792265</v>
+        <v>119788482</v>
       </c>
       <c r="B75" t="n">
-        <v>89256</v>
+        <v>89292</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8523,48 +8526,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6268</v>
+        <v>6286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>481044</v>
+        <v>481092</v>
       </c>
       <c r="R75" t="n">
-        <v>6784736</v>
+        <v>6784610</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8602,29 +8598,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119787167</v>
+        <v>119787790</v>
       </c>
       <c r="B76" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8637,21 +8632,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8661,10 +8656,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>481197</v>
+        <v>481260</v>
       </c>
       <c r="R76" t="n">
-        <v>6784509</v>
+        <v>6784612</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8723,10 +8718,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119788082</v>
+        <v>119787715</v>
       </c>
       <c r="B77" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8739,21 +8734,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8763,10 +8758,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>481144</v>
+        <v>481274</v>
       </c>
       <c r="R77" t="n">
-        <v>6784602</v>
+        <v>6784652</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8825,10 +8820,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119789001</v>
+        <v>119787021</v>
       </c>
       <c r="B78" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8841,21 +8836,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8865,10 +8860,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>481138</v>
+        <v>481048</v>
       </c>
       <c r="R78" t="n">
-        <v>6784747</v>
+        <v>6784513</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8927,10 +8922,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119787771</v>
+        <v>119788550</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>90084</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8939,38 +8934,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>256703</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>481276</v>
+        <v>481050</v>
       </c>
       <c r="R79" t="n">
-        <v>6784646</v>
+        <v>6784604</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9000,9 +9004,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9017,22 +9031,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119787094</v>
+        <v>119787002</v>
       </c>
       <c r="B80" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9041,25 +9055,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9069,10 +9083,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>481175</v>
+        <v>481114</v>
       </c>
       <c r="R80" t="n">
-        <v>6784516</v>
+        <v>6784523</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9131,10 +9145,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119787715</v>
+        <v>119789077</v>
       </c>
       <c r="B81" t="n">
-        <v>91902</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9147,21 +9161,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9171,10 +9185,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>481274</v>
+        <v>481052</v>
       </c>
       <c r="R81" t="n">
-        <v>6784652</v>
+        <v>6784759</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9221,19 +9235,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119786882</v>
+        <v>119789001</v>
       </c>
       <c r="B82" t="n">
         <v>91874</v>
@@ -9273,10 +9287,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>481048</v>
+        <v>481138</v>
       </c>
       <c r="R82" t="n">
-        <v>6784513</v>
+        <v>6784747</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9335,10 +9349,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119788776</v>
+        <v>119788908</v>
       </c>
       <c r="B83" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9351,21 +9365,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9375,10 +9389,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>481179</v>
+        <v>481028</v>
       </c>
       <c r="R83" t="n">
-        <v>6784744</v>
+        <v>6784697</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9437,10 +9451,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119788782</v>
+        <v>119787848</v>
       </c>
       <c r="B84" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9449,47 +9463,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>481195</v>
+        <v>481187</v>
       </c>
       <c r="R84" t="n">
-        <v>6784739</v>
+        <v>6784640</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9519,19 +9524,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9546,22 +9541,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119786836</v>
+        <v>119787094</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9570,25 +9565,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9598,10 +9593,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>481049</v>
+        <v>481175</v>
       </c>
       <c r="R85" t="n">
-        <v>6784514</v>
+        <v>6784516</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9660,10 +9655,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119788305</v>
+        <v>119788082</v>
       </c>
       <c r="B86" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9676,37 +9671,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>481083</v>
+        <v>481144</v>
       </c>
       <c r="R86" t="n">
-        <v>6784643</v>
+        <v>6784602</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9733,19 +9728,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9760,22 +9745,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119787665</v>
+        <v>119788519</v>
       </c>
       <c r="B87" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9784,25 +9769,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9812,10 +9797,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>481287</v>
+        <v>481087</v>
       </c>
       <c r="R87" t="n">
-        <v>6784633</v>
+        <v>6784724</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9874,10 +9859,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119787935</v>
+        <v>119788104</v>
       </c>
       <c r="B88" t="n">
-        <v>78542</v>
+        <v>8432</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9886,38 +9871,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>481160</v>
+        <v>481122</v>
       </c>
       <c r="R88" t="n">
-        <v>6784611</v>
+        <v>6784602</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9964,22 +9954,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119788033</v>
+        <v>119787740</v>
       </c>
       <c r="B89" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9988,25 +9978,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10016,10 +10006,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>481181</v>
+        <v>481276</v>
       </c>
       <c r="R89" t="n">
-        <v>6784644</v>
+        <v>6784646</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10066,22 +10056,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119787002</v>
+        <v>119788565</v>
       </c>
       <c r="B90" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10090,25 +10080,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10118,10 +10108,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>481114</v>
+        <v>481108</v>
       </c>
       <c r="R90" t="n">
-        <v>6784523</v>
+        <v>6784708</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10180,10 +10170,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119788565</v>
+        <v>119788774</v>
       </c>
       <c r="B91" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10192,38 +10182,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>481108</v>
+        <v>481195</v>
       </c>
       <c r="R91" t="n">
-        <v>6784708</v>
+        <v>6784739</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10253,9 +10243,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10270,12 +10270,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 34474-2024 artfynd.xlsx
+++ b/artfynd/A 34474-2024 artfynd.xlsx
@@ -5210,10 +5210,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119788782</v>
+        <v>119786882</v>
       </c>
       <c r="B44" t="n">
-        <v>91881</v>
+        <v>91874</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5226,43 +5226,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Väster Unnån, Väster Unnån, Dlr</t>
+          <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>481195</v>
+        <v>481048</v>
       </c>
       <c r="R44" t="n">
-        <v>6784739</v>
+        <v>6784513</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,19 +5283,9 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,22 +5300,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Frida Blixt</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119788305</v>
+        <v>119788782</v>
       </c>
       <c r="B45" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5347,37 +5328,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>481083</v>
+        <v>481195</v>
       </c>
       <c r="R45" t="n">
-        <v>6784643</v>
+        <v>6784739</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,7 +5396,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5406,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5433,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119788766</v>
+        <v>119788305</v>
       </c>
       <c r="B46" t="n">
-        <v>78543</v>
+        <v>91902</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5459,37 +5449,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230405</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Unnan, Unnan, Dlr</t>
+          <t>Väster Unnån, Väster Unnån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>481176</v>
+        <v>481083</v>
       </c>
       <c r="R46" t="n">
-        <v>6784737</v>
+        <v>6784643</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5516,9 +5506,19 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5533,22 +5533,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119786882</v>
+        <v>119788766</v>
       </c>
       <c r="B47" t="n">
-        <v>91874</v>
+        <v>78543</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>230405</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>481048</v>
+        <v>481176</v>
       </c>
       <c r="R47" t="n">
-        <v>6784513</v>
+        <v>6784737</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7670,10 +7670,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119787544</v>
+        <v>119788033</v>
       </c>
       <c r="B67" t="n">
-        <v>8432</v>
+        <v>91874</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7682,47 +7682,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>2059</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>481291</v>
+        <v>481181</v>
       </c>
       <c r="R67" t="n">
-        <v>6784590</v>
+        <v>6784644</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7752,50 +7743,39 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119788033</v>
+        <v>119787544</v>
       </c>
       <c r="B68" t="n">
-        <v>91874</v>
+        <v>8432</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7804,38 +7784,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2059</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Unnan, Unnan, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>481181</v>
+        <v>481291</v>
       </c>
       <c r="R68" t="n">
-        <v>6784644</v>
+        <v>6784590</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7865,39 +7854,50 @@
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-16</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119786836</v>
+        <v>119788776</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>91874</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7910,21 +7910,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7934,10 +7934,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>481049</v>
+        <v>481179</v>
       </c>
       <c r="R69" t="n">
-        <v>6784514</v>
+        <v>6784744</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7996,7 +7996,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119788776</v>
+        <v>119789105</v>
       </c>
       <c r="B70" t="n">
         <v>91874</v>
@@ -8036,10 +8036,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>481179</v>
+        <v>481038</v>
       </c>
       <c r="R70" t="n">
-        <v>6784744</v>
+        <v>6784721</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8098,10 +8098,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119789105</v>
+        <v>119786836</v>
       </c>
       <c r="B71" t="n">
-        <v>91874</v>
+        <v>78542</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8114,21 +8114,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>481038</v>
+        <v>481049</v>
       </c>
       <c r="R71" t="n">
-        <v>6784721</v>
+        <v>6784514</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
